--- a/plantilla_sitio.xlsx
+++ b/plantilla_sitio.xlsx
@@ -464,121 +464,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH21"/>
+  <dimension ref="A1:CW41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="33" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="35" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="50" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="41" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
-    <col width="27" customWidth="1" min="25" max="25"/>
-    <col width="21" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="24" customWidth="1" min="28" max="28"/>
-    <col width="25" customWidth="1" min="29" max="29"/>
-    <col width="25" customWidth="1" min="30" max="30"/>
-    <col width="18" customWidth="1" min="31" max="31"/>
-    <col width="19" customWidth="1" min="32" max="32"/>
-    <col width="24" customWidth="1" min="33" max="33"/>
-    <col width="22" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="18" customWidth="1" min="36" max="36"/>
-    <col width="33" customWidth="1" min="37" max="37"/>
-    <col width="29" customWidth="1" min="38" max="38"/>
-    <col width="29" customWidth="1" min="39" max="39"/>
-    <col width="16" customWidth="1" min="40" max="40"/>
-    <col width="19" customWidth="1" min="41" max="41"/>
-    <col width="23" customWidth="1" min="42" max="42"/>
-    <col width="20" customWidth="1" min="43" max="43"/>
-    <col width="31" customWidth="1" min="44" max="44"/>
-    <col width="32" customWidth="1" min="45" max="45"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="50" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="24" customWidth="1" min="30" max="30"/>
+    <col width="27" customWidth="1" min="31" max="31"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="25" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="23" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="43" customWidth="1" min="39" max="39"/>
+    <col width="27" customWidth="1" min="40" max="40"/>
+    <col width="16" customWidth="1" min="41" max="41"/>
+    <col width="19" customWidth="1" min="42" max="42"/>
+    <col width="23" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="15" customWidth="1" min="45" max="45"/>
     <col width="15" customWidth="1" min="46" max="46"/>
     <col width="15" customWidth="1" min="47" max="47"/>
-    <col width="15" customWidth="1" min="48" max="48"/>
-    <col width="29" customWidth="1" min="49" max="49"/>
-    <col width="15" customWidth="1" min="50" max="50"/>
+    <col width="24" customWidth="1" min="48" max="48"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
+    <col width="19" customWidth="1" min="50" max="50"/>
     <col width="22" customWidth="1" min="51" max="51"/>
-    <col width="23" customWidth="1" min="52" max="52"/>
-    <col width="29" customWidth="1" min="53" max="53"/>
-    <col width="34" customWidth="1" min="54" max="54"/>
-    <col width="32" customWidth="1" min="55" max="55"/>
-    <col width="24" customWidth="1" min="56" max="56"/>
-    <col width="36" customWidth="1" min="57" max="57"/>
-    <col width="28" customWidth="1" min="58" max="58"/>
+    <col width="16" customWidth="1" min="52" max="52"/>
+    <col width="16" customWidth="1" min="53" max="53"/>
+    <col width="18" customWidth="1" min="54" max="54"/>
+    <col width="25" customWidth="1" min="55" max="55"/>
+    <col width="22" customWidth="1" min="56" max="56"/>
+    <col width="15" customWidth="1" min="57" max="57"/>
+    <col width="15" customWidth="1" min="58" max="58"/>
     <col width="15" customWidth="1" min="59" max="59"/>
-    <col width="43" customWidth="1" min="60" max="60"/>
-    <col width="16" customWidth="1" min="61" max="61"/>
-    <col width="17" customWidth="1" min="62" max="62"/>
-    <col width="16" customWidth="1" min="63" max="63"/>
-    <col width="35" customWidth="1" min="64" max="64"/>
-    <col width="15" customWidth="1" min="65" max="65"/>
-    <col width="22" customWidth="1" min="66" max="66"/>
-    <col width="22" customWidth="1" min="67" max="67"/>
-    <col width="34" customWidth="1" min="68" max="68"/>
-    <col width="33" customWidth="1" min="69" max="69"/>
-    <col width="15" customWidth="1" min="70" max="70"/>
-    <col width="39" customWidth="1" min="71" max="71"/>
-    <col width="37" customWidth="1" min="72" max="72"/>
+    <col width="15" customWidth="1" min="60" max="60"/>
+    <col width="27" customWidth="1" min="61" max="61"/>
+    <col width="15" customWidth="1" min="62" max="62"/>
+    <col width="27" customWidth="1" min="63" max="63"/>
+    <col width="31" customWidth="1" min="64" max="64"/>
+    <col width="34" customWidth="1" min="65" max="65"/>
+    <col width="31" customWidth="1" min="66" max="66"/>
+    <col width="31" customWidth="1" min="67" max="67"/>
+    <col width="31" customWidth="1" min="68" max="68"/>
+    <col width="23" customWidth="1" min="69" max="69"/>
+    <col width="28" customWidth="1" min="70" max="70"/>
+    <col width="22" customWidth="1" min="71" max="71"/>
+    <col width="30" customWidth="1" min="72" max="72"/>
     <col width="31" customWidth="1" min="73" max="73"/>
-    <col width="15" customWidth="1" min="74" max="74"/>
-    <col width="15" customWidth="1" min="75" max="75"/>
-    <col width="38" customWidth="1" min="76" max="76"/>
-    <col width="34" customWidth="1" min="77" max="77"/>
-    <col width="34" customWidth="1" min="78" max="78"/>
-    <col width="50" customWidth="1" min="79" max="79"/>
-    <col width="16" customWidth="1" min="80" max="80"/>
-    <col width="37" customWidth="1" min="81" max="81"/>
-    <col width="45" customWidth="1" min="82" max="82"/>
-    <col width="15" customWidth="1" min="83" max="83"/>
-    <col width="20" customWidth="1" min="84" max="84"/>
-    <col width="29" customWidth="1" min="85" max="85"/>
-    <col width="15" customWidth="1" min="86" max="86"/>
-    <col width="21" customWidth="1" min="87" max="87"/>
-    <col width="28" customWidth="1" min="88" max="88"/>
-    <col width="25" customWidth="1" min="89" max="89"/>
-    <col width="34" customWidth="1" min="90" max="90"/>
-    <col width="32" customWidth="1" min="91" max="91"/>
-    <col width="37" customWidth="1" min="92" max="92"/>
-    <col width="15" customWidth="1" min="93" max="93"/>
-    <col width="15" customWidth="1" min="94" max="94"/>
-    <col width="24" customWidth="1" min="95" max="95"/>
-    <col width="24" customWidth="1" min="96" max="96"/>
-    <col width="15" customWidth="1" min="97" max="97"/>
-    <col width="26" customWidth="1" min="98" max="98"/>
-    <col width="45" customWidth="1" min="99" max="99"/>
-    <col width="38" customWidth="1" min="100" max="100"/>
+    <col width="41" customWidth="1" min="74" max="74"/>
+    <col width="27" customWidth="1" min="75" max="75"/>
+    <col width="31" customWidth="1" min="76" max="76"/>
+    <col width="30" customWidth="1" min="77" max="77"/>
+    <col width="15" customWidth="1" min="78" max="78"/>
+    <col width="22" customWidth="1" min="79" max="79"/>
+    <col width="28" customWidth="1" min="80" max="80"/>
+    <col width="23" customWidth="1" min="81" max="81"/>
+    <col width="35" customWidth="1" min="82" max="82"/>
+    <col width="34" customWidth="1" min="83" max="83"/>
+    <col width="32" customWidth="1" min="84" max="84"/>
+    <col width="23" customWidth="1" min="85" max="85"/>
+    <col width="35" customWidth="1" min="86" max="86"/>
+    <col width="17" customWidth="1" min="87" max="87"/>
+    <col width="29" customWidth="1" min="88" max="88"/>
+    <col width="38" customWidth="1" min="89" max="89"/>
+    <col width="38" customWidth="1" min="90" max="90"/>
+    <col width="27" customWidth="1" min="91" max="91"/>
+    <col width="19" customWidth="1" min="92" max="92"/>
+    <col width="26" customWidth="1" min="93" max="93"/>
+    <col width="25" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="33" customWidth="1" min="97" max="97"/>
+    <col width="15" customWidth="1" min="98" max="98"/>
+    <col width="39" customWidth="1" min="99" max="99"/>
+    <col width="16" customWidth="1" min="100" max="100"/>
     <col width="15" customWidth="1" min="101" max="101"/>
-    <col width="22" customWidth="1" min="102" max="102"/>
-    <col width="28" customWidth="1" min="103" max="103"/>
-    <col width="27" customWidth="1" min="104" max="104"/>
-    <col width="36" customWidth="1" min="105" max="105"/>
-    <col width="24" customWidth="1" min="106" max="106"/>
-    <col width="15" customWidth="1" min="107" max="107"/>
-    <col width="24" customWidth="1" min="108" max="108"/>
-    <col width="24" customWidth="1" min="109" max="109"/>
-    <col width="31" customWidth="1" min="110" max="110"/>
-    <col width="16" customWidth="1" min="111" max="111"/>
-    <col width="15" customWidth="1" min="112" max="112"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -599,545 +588,490 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>BOMBA DE TRASIEGO HACIA STARnD</t>
+          <t>SERVICIO</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>SERVICIO</t>
+          <t>FUNCIÓN</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>FUNCIÓN</t>
+          <t>DESCRIPCIÓN DE OPERACIÓN</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>DESCRIPCIÓN DE OPERACIÓN</t>
+          <t>FLUIDO</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>FLUIDO</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>DENSIDAD (g/mL)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TEMPERATURA MÁXIMA FLUIDO (°C)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TIPO DE TANQUE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>DIÁMETRO TOTAL (m)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ALTURA TOTAL (m)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ALTURA ÚTIL (m)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>VOLUMEN TOTAL (m3)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>VOLUMEN ÚTIL (m3)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TIPO DE BOMBA</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>CAUDAL OPERACIÓN (m3/h)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>PRESIÓN MAXIMA BOMBA (PSI)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>POTENCIA NOMINAL (HP)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>VELOCIDAD BOMBA (rpm)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>VOLTAJE (V)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FRECUENCIA (Hz)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>PROTECCIÓN</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>DIAMETRO IMPULSOR (mm)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>CONEXIÓN</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>TIPO DE ARRANQUE</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>MARCA/ MODELO</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>CANTIDAD DE DIFUSORES</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>DENSIDAD APROXIMADA g/m3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>FLUJO DE DISEÑO (SCFM)</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ENTRADA DE AIRE</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>TIPO DE SOPORTE</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>FORMA</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>DIAMETRO (mm)</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ESPESOR (mm)</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>GRAVEDAD ESPECIFICA (SIN BIOMASA) (kg/L)</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>AREA SUPERFICIAL (m2/m3)</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>CAPACIDAD (L)</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>ÁREA TOTAL (cm2)</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>ALTURA EFECTIVA (cm)</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>ALTURA TOTAL (cm)</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>ANCHO (cm)</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>LARGO (cm)</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>ALTURA (cm)</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>DIÁMETRO INTERNO (mm)</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>ALTURA DEL CUERPO (mm)</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>TEMPERATURA (°C)</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>CAUDAL MÁXIMO (CFM)</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>PRESIÓN (PSI)</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>POTENCIA (HP)</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>VELOCIDAD (rpm)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>AMPERAJE CON CARGA (A)</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>VACÍO MÁXIMO (mBar)</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>A (cm)</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>B (cm)</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>C (cm)</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>D (cm)</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
           <t>DENSIDAD APROXIMADA g/ml</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>TEMPERATURA MÁXIMA FLUIDO (°C)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>TIPO</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>CAUDAL MÁXIMO (m3 /h)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>IMPELLERS</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>NÚMERO DE ETAPAS</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ALTURA MÁXIMA A CAUDAL MÁXIMO(m)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>VELOCIDAD MOTOR (RPM)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>POTENCIA (HP)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>VOLTAJE (V)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>FRECUENCIA</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>MATERIAL</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>CANTIDAD</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>DIÁMETRO POR FILTRO (in)</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>TASA DE FILTRACIÓN (m3/m2/d)</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>TASA DE RETROLAVADO (m3/m2/min)</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>PESO DE GRAVA 1/4"-1/8" (Kg)</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>PESO DE GRAVA 1/2"-1/4" (Kg)</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>PESO DE GRAVA 3/4"-1/2" (Kg)</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>PESO DE TORPEDO (Kg)</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>PESO DE ARENA 0.45mm (Kg)</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>PESO ANTRACITA (Kg)</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>ALTURA LIBRE DEL FILTRO (m)</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>ALTURA TOTAL DEL FILTRO (mm)</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>EXPANSIÓN DEL LECHO EN RETROLAVADO (%)</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>TIEMPO DE CONTACTO (min)</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>PESO DE TORPEDO DELGADO (kg)</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>PESO DE TORPEDO GRUESO (kg)</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>VOL CAG (m3)</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>CAUDAL MÁXIMO (LPM)</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>CAUDAL DE OPERACIÓN (LPM)</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>PRESIÓN MÁXIMA (PSI)</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>PRESION DE AIRE COMPRIMIDO (PSI)</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>ALTURA MÁXIMA DE ASPIRACIÓN (m)</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>CONSUMO MÁXIMO DE AIRE (SCFM)</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>ENTRADA DE AIRE (mm)</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>ENTRADA Y SALIDA DEL FLUIDO (mm)</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>MARCA / MODELO</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>BOMBA STANDBY DE TRASIEGO HACIA STARnD</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>SEDIMENTADOR DAF</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>VISCOSIDAD APROXIMADA cp</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>FLUJO DISEÑO (L/s)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>CAPACIDAD (m3)</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>DIÁMETRO INTERNO (mm)</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>ALTURA DEL CUERPO (mm)</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>BOMBA DE RECIRCULACIÓN</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>DENSIDAD (g/mL)</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>TEMPERATURA (°C)</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>CAUDAL MÁXIMO (L/min)</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>NUMERO DE IMPELLERS</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>MÁXIMA PRESIÓN (mca)</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>FRECUENCIA (Hz)</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>MARCA/ MODELO</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>TANQUE DE AGUA CLARIFICADA</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>DENSIDAD APROXIMADA (g/mL)</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>CAPACIDAD (L)</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>ÁREA TOTAL (cm2)</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>ALTURA EFECTIVA (cm)</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>ALTURA TOTAL (cm)</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>TANQUE DE RECEPCIÓN DE LODOS</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>CONCENTRACIÓN DE LODOS (mg/L)</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>ANCHO (cm)</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>LARGO (cm)</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>ALTURA (cm)</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>BOMBA DE TRASIEGO DE LODOS</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>600-P-01</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>CAUDAL MÁXIMO (LPM)</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>PRESIÓN MÁXIMA (PSI)</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>PRESIÓN DE OPERACIÓN (PSI)</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>ALTURA MÁXIMA DE ASPIRACIÓN (m)</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>CONSUMO MÁXIMO DE AIRE (SCFM)</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>ENTRADA DE AIRE (NTP)</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>ENTRADA Y SALIDA DEL FLUIDO (NPT)</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>BOMBA PARA TRASIEGO LODOS</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>600-P-02</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>TANQUE PARA ALMACENAMIENTO DE COAGULANTE</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>CONCENTRACIÓN</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>TIPO DE TANQUE</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>DIAMETRO (cm)</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>BONBA DOSIFICADORA DE COAGULANTE</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>800-P-01</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>ÁREA DE FILTRADO REAL (m2)</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>DIMENSIÓN INTERIOR DE LA PLACA (mm)</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>DIMENSIÓN EXTERIOR DE LA PLACA (mm)</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>ESPESOR DE LA PLACA (mm)</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>NÚMERO DE PLACAS</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>Presión de cierre (Mpa)</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>Precisión del filtrado</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>CONCENTRACIÓN (g/L)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>CAUDAL MÁXIMO (L/h)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>PRESIÓN DE TRABAJO MÁXIMA (bar)</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>GRADO DE PROTECCIÓN (IEC 34-5)</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>POTENCIA (W)</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>RANGO DE TEMPERATURA DE TRABAJO (°C)</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>TANQUE PARA ALMACENAMIENTO DE SODA</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>BOMBA DOSIFICADORA PARA SODA</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>801-P-01A</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>801-P-01B</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>TANQUE DE PREPARACIÓN DE FLOCULANTE</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>BOMBA NEUMÁTICA PARA FLOCULANTE</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>NIVEL DE SINIDO A 100 PSI (dBA)</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>TANQUE DE PREPARACIÓN Y ALMACENAMIENTO DE DESHIDRATANTE</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>DIAMETRO (Cm)</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>BOMBA NEUMÁTICA PARA DESHIDRATANTE</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>MOTOR REDUCTOR AGITADOR DE TANQUE DE LODOS</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>600-M-01</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>VELOCIDAD (r/min)</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>ÍNDICE REDUCCIÓN TOTAL (i)</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>Ma max (Nm)</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>PAR DE SALIDA (Nm)</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>FACTOR DE SERVICIO SEW FB</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>POSICIÓN DE MONTAJE IM</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>POS. CAJA BORNAS / ENTR. CABLES</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>LUBRICANTE / CANTIDAD (L)</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>CAPA DE PINTURA</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>REDUCTOR</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>EJE HUECO</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>DISEÑO</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>CAPERUZA DE SEGURIDAD</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>BRIDA (mm)</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>VARIANTE DE VENTILACIÓN</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>ESTADO DE ENTREGA</t>
-        </is>
-      </c>
       <c r="CV1" s="1" t="inlineStr">
         <is>
-          <t>HOJA DIAMETRO AGUJERO TAPON ROSCADO</t>
+          <t>Ficha Técnica</t>
         </is>
       </c>
       <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>MOTOR</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>POTENCIA MOTOR (kW)</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>FRECUENCIA DEL MOTOR (Hz)</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>TIO DE SERVICIO S1 - S10</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>TENSIÓN MOTOR (V) / CONEXIÓN</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>CORRIENTE NOMINAL (A)</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>Cos phi</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>ESQUEMA DE CONEXIONES</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>TIPO AISLAMIENTO / IP</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>EFICIENCIA 50/75/100% Pn [%]</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>Ficha Técnica</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>Curva</t>
         </is>
@@ -1146,38 +1080,38 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>100-P-01 A</t>
+          <t>100-TK-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EQUIPOS</t>
+          <t>TANQUES</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>JCSA</t>
+          <t>Homogenización ARnD</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tratamiento de agua residual NO doméstica</t>
+          <t>Homogenización de caudales, cargas, pH y temperatura</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Trasiego de agua cruda desde el 100-TK-01 al 200-PS-01</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>ARnD</t>
+          <t>6 - 8</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1187,69 +1121,49 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>&gt;5</t>
+          <t>&lt;30</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Cilíndrico Vertical con Fondo Plano</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Centrifuga Horizontal</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>3~440</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>Cuerpo/Impulsor /Carcasa AISI 304</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Ebara DWO 4006</t>
-        </is>
-      </c>
+          <t>PRFV</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="n"/>
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="n"/>
@@ -1329,49 +1243,42 @@
       <c r="CU2" s="2" t="n"/>
       <c r="CV2" s="2" t="n"/>
       <c r="CW2" s="2" t="n"/>
-      <c r="CX2" s="2" t="n"/>
-      <c r="CY2" s="2" t="n"/>
-      <c r="CZ2" s="2" t="n"/>
-      <c r="DA2" s="2" t="n"/>
-      <c r="DB2" s="2" t="n"/>
-      <c r="DC2" s="2" t="n"/>
-      <c r="DD2" s="2" t="n"/>
-      <c r="DE2" s="2" t="n"/>
-      <c r="DF2" s="2" t="n"/>
-      <c r="DG2" s="2" t="n"/>
-      <c r="DH2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>100-P-01 B</t>
+          <t>100-TK-02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>EQUIPOS</t>
+          <t>TANQUES</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Homogenización ARnD</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tratamiento de agua residual NO doméstica</t>
+          <t>Homogenización de caudales, cargas, pH y temperatura</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Trasiego de agua cruda desde el 100-TK-01 al 200-PS-01</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>ARnD</t>
+          <t>6 - 8</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -1381,74 +1288,50 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>&gt;5</t>
+          <t>&lt;30</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Cilíndrico Vertical con Fondo Plano</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Centrifuga Horizontal</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>3~440</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>Cuerpo/Impulsor /Carcasa AISI 304</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Ebara DWO 4006</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
+          <t>PRFV</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="n"/>
       <c r="Z3" s="2" t="n"/>
@@ -1527,22 +1410,11 @@
       <c r="CU3" s="2" t="n"/>
       <c r="CV3" s="2" t="n"/>
       <c r="CW3" s="2" t="n"/>
-      <c r="CX3" s="2" t="n"/>
-      <c r="CY3" s="2" t="n"/>
-      <c r="CZ3" s="2" t="n"/>
-      <c r="DA3" s="2" t="n"/>
-      <c r="DB3" s="2" t="n"/>
-      <c r="DC3" s="2" t="n"/>
-      <c r="DD3" s="2" t="n"/>
-      <c r="DE3" s="2" t="n"/>
-      <c r="DF3" s="2" t="n"/>
-      <c r="DG3" s="2" t="n"/>
-      <c r="DH3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>200-PS-01</t>
+          <t>100-P-01A</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1551,86 +1423,111 @@
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Bomba centrifuga horizontal</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Celda de Flotación de aire disuelto</t>
+          <t>Trasiego de ARnD al DAF / Trasiego de ARnD de los reactores MBBR al DAF</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Separación sólido - Liquido del licor mezcla</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Agua Residual</t>
+          <t>6 - 8</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6.0 - 9.0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="n"/>
-      <c r="T4" s="2" t="n"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Cuerpo de la bomba, impulsor, cobertura del sello, carcasa AISI 304. AISI 303 (parte en contacto con líquido).</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Centrifuga horizontal</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>PRFV</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="n"/>
-      <c r="W4" s="2" t="n"/>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>JCSA</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>IP55</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>Succión: 2½″ NPT hembra
+Descarga: 2″ NPT hembra</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>Directo-en-línea (DOL)</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>CDX 70/076</t>
         </is>
       </c>
       <c r="AD4" s="2" t="n"/>
@@ -1705,22 +1602,11 @@
       <c r="CU4" s="2" t="n"/>
       <c r="CV4" s="2" t="n"/>
       <c r="CW4" s="2" t="n"/>
-      <c r="CX4" s="2" t="n"/>
-      <c r="CY4" s="2" t="n"/>
-      <c r="CZ4" s="2" t="n"/>
-      <c r="DA4" s="2" t="n"/>
-      <c r="DB4" s="2" t="n"/>
-      <c r="DC4" s="2" t="n"/>
-      <c r="DD4" s="2" t="n"/>
-      <c r="DE4" s="2" t="n"/>
-      <c r="DF4" s="2" t="n"/>
-      <c r="DG4" s="2" t="n"/>
-      <c r="DH4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>200-P-01A</t>
+          <t>100-P-01B</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1729,112 +1615,121 @@
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Bomba centrifuga horizontal</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bomba microburbuja</t>
+          <t>Trasiego de ARnD al DAF / Trasiego de ARnD de los reactores MBBR al DAF</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Recirculación interna con microburbuja DAF</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Agua clarificada</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Centrifuga</t>
-        </is>
-      </c>
+      <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
+          <t>Cuerpo de la bomba, impulsor, cobertura del sello, carcasa AISI 304. AISI 303 (parte en contacto con líquido).</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Centrifuga horizontal</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>3~ 440 V</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="n"/>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>Impulsor y Carcasa en SS304</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="n"/>
-      <c r="W5" s="2" t="n"/>
-      <c r="X5" s="2" t="n"/>
-      <c r="Y5" s="2" t="n"/>
-      <c r="Z5" s="2" t="n"/>
-      <c r="AA5" s="2" t="n"/>
-      <c r="AB5" s="2" t="n"/>
-      <c r="AC5" s="2" t="n"/>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG5" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AH5" s="2" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="AI5" s="2" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AK5" s="2" t="inlineStr">
-        <is>
-          <t>EBARA Matrix 3 4T6/1.3</t>
-        </is>
-      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>Succión: 2½″ NPT hembra
+Descarga: 2″ NPT hembra</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>Directo-en-línea (DOL)</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>CDX 70/076</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="n"/>
+      <c r="AE5" s="2" t="n"/>
+      <c r="AF5" s="2" t="n"/>
+      <c r="AG5" s="2" t="n"/>
+      <c r="AH5" s="2" t="n"/>
+      <c r="AI5" s="2" t="n"/>
+      <c r="AJ5" s="2" t="n"/>
+      <c r="AK5" s="2" t="n"/>
       <c r="AL5" s="2" t="n"/>
       <c r="AM5" s="2" t="n"/>
       <c r="AN5" s="2" t="n"/>
@@ -1899,22 +1794,11 @@
       <c r="CU5" s="2" t="n"/>
       <c r="CV5" s="2" t="n"/>
       <c r="CW5" s="2" t="n"/>
-      <c r="CX5" s="2" t="n"/>
-      <c r="CY5" s="2" t="n"/>
-      <c r="CZ5" s="2" t="n"/>
-      <c r="DA5" s="2" t="n"/>
-      <c r="DB5" s="2" t="n"/>
-      <c r="DC5" s="2" t="n"/>
-      <c r="DD5" s="2" t="n"/>
-      <c r="DE5" s="2" t="n"/>
-      <c r="DF5" s="2" t="n"/>
-      <c r="DG5" s="2" t="n"/>
-      <c r="DH5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>200-P-01B</t>
+          <t>200-P-02A</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1923,112 +1807,121 @@
         </is>
       </c>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Bomba centrifuga horizontal</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Bomba microburbuja</t>
+          <t>Trasiego de ARnD a reactores biológicos ó filtración</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Recirculación interna con microburbuja DAF</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Agua clarificada</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Centrifuga</t>
-        </is>
-      </c>
+      <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
+          <t>Cuerpo de la bomba, impulsor, cobertura del sello, carcasa AISI 304. AISI 303 (parte en contacto con líquido).</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Centrifuga horizontal</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>3~ 440 V</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="n"/>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>Impulsor y Carcasa en SS304</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="n"/>
-      <c r="W6" s="2" t="n"/>
-      <c r="X6" s="2" t="n"/>
-      <c r="Y6" s="2" t="n"/>
-      <c r="Z6" s="2" t="n"/>
-      <c r="AA6" s="2" t="n"/>
-      <c r="AB6" s="2" t="n"/>
-      <c r="AC6" s="2" t="n"/>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG6" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AH6" s="2" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="AI6" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AK6" s="2" t="inlineStr">
-        <is>
-          <t>EBARA Matrix 3 4T6/1.3</t>
-        </is>
-      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>Succión: 2½″ NPT hembra
+Descarga: 2″ NPT hembra</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>Directo-en-línea (DOL)</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>CDX 70/076</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="n"/>
+      <c r="AE6" s="2" t="n"/>
+      <c r="AF6" s="2" t="n"/>
+      <c r="AG6" s="2" t="n"/>
+      <c r="AH6" s="2" t="n"/>
+      <c r="AI6" s="2" t="n"/>
+      <c r="AJ6" s="2" t="n"/>
+      <c r="AK6" s="2" t="n"/>
       <c r="AL6" s="2" t="n"/>
       <c r="AM6" s="2" t="n"/>
       <c r="AN6" s="2" t="n"/>
@@ -2093,84 +1986,126 @@
       <c r="CU6" s="2" t="n"/>
       <c r="CV6" s="2" t="n"/>
       <c r="CW6" s="2" t="n"/>
-      <c r="CX6" s="2" t="n"/>
-      <c r="CY6" s="2" t="n"/>
-      <c r="CZ6" s="2" t="n"/>
-      <c r="DA6" s="2" t="n"/>
-      <c r="DB6" s="2" t="n"/>
-      <c r="DC6" s="2" t="n"/>
-      <c r="DD6" s="2" t="n"/>
-      <c r="DE6" s="2" t="n"/>
-      <c r="DF6" s="2" t="n"/>
-      <c r="DG6" s="2" t="n"/>
-      <c r="DH6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>200-TK-01</t>
+          <t>200-P-02B</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TANQUES</t>
+          <t>EQUIPOS</t>
         </is>
       </c>
       <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Bomba centrifuga horizontal</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Recepción de agua</t>
+          <t>Trasiego de ARnD a reactores biológicos ó filtración</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Recepción de agua clarificada para microburbuja</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Agua clarificada</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n"/>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6.0-8.0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="n"/>
-      <c r="R7" s="2" t="n"/>
-      <c r="S7" s="2" t="n"/>
-      <c r="T7" s="2" t="n"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Cuerpo de la bomba, impulsor, cobertura del sello, carcasa AISI 304. AISI 303 (parte en contacto con líquido).</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Centrifuga horizontal</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>POLIETILENO</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="n"/>
-      <c r="W7" s="2" t="n"/>
-      <c r="X7" s="2" t="n"/>
-      <c r="Y7" s="2" t="n"/>
-      <c r="Z7" s="2" t="n"/>
-      <c r="AA7" s="2" t="n"/>
-      <c r="AB7" s="2" t="n"/>
-      <c r="AC7" s="2" t="n"/>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>Succión: 2½″ NPT hembra
+Descarga: 2″ NPT hembra</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>Directo-en-línea (DOL)</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>CDX 70/076</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="n"/>
       <c r="AE7" s="2" t="n"/>
       <c r="AF7" s="2" t="n"/>
@@ -2179,36 +2114,12 @@
       <c r="AI7" s="2" t="n"/>
       <c r="AJ7" s="2" t="n"/>
       <c r="AK7" s="2" t="n"/>
-      <c r="AL7" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="AM7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AN7" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="AO7" s="2" t="inlineStr">
-        <is>
-          <t>12100</t>
-        </is>
-      </c>
-      <c r="AP7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AQ7" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+      <c r="AL7" s="2" t="n"/>
+      <c r="AM7" s="2" t="n"/>
+      <c r="AN7" s="2" t="n"/>
+      <c r="AO7" s="2" t="n"/>
+      <c r="AP7" s="2" t="n"/>
+      <c r="AQ7" s="2" t="n"/>
       <c r="AR7" s="2" t="n"/>
       <c r="AS7" s="2" t="n"/>
       <c r="AT7" s="2" t="n"/>
@@ -2267,84 +2178,128 @@
       <c r="CU7" s="2" t="n"/>
       <c r="CV7" s="2" t="n"/>
       <c r="CW7" s="2" t="n"/>
-      <c r="CX7" s="2" t="n"/>
-      <c r="CY7" s="2" t="n"/>
-      <c r="CZ7" s="2" t="n"/>
-      <c r="DA7" s="2" t="n"/>
-      <c r="DB7" s="2" t="n"/>
-      <c r="DC7" s="2" t="n"/>
-      <c r="DD7" s="2" t="n"/>
-      <c r="DE7" s="2" t="n"/>
-      <c r="DF7" s="2" t="n"/>
-      <c r="DG7" s="2" t="n"/>
-      <c r="DH7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600-TK-01</t>
+          <t>200-P-01A</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TANQUES</t>
+          <t>EQUIPOS</t>
         </is>
       </c>
       <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Bomba centrifuga horizontal</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Lodos Biologicos</t>
+          <t>Recirculación de agua clarificada para microburbuja</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Recepción de lodos</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Lodo</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n"/>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5.0-9.0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n"/>
-      <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2" t="n"/>
-      <c r="T8" s="2" t="n"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Cuerpo AISI 304 
+Impulsor AISI 304
+Carcasa AISI304</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Centrifuga horizontal</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>POLIETILENO</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="n"/>
-      <c r="W8" s="2" t="n"/>
-      <c r="X8" s="2" t="n"/>
-      <c r="Y8" s="2" t="n"/>
-      <c r="Z8" s="2" t="n"/>
-      <c r="AA8" s="2" t="n"/>
-      <c r="AB8" s="2" t="n"/>
-      <c r="AC8" s="2" t="n"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>0.8627450980392157</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>Succión: 2½″ NPT hembra
+Descarga: 2″ NPT hembra</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>Directo-en-línea (DOL)</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>2CDX 70/306</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="n"/>
       <c r="AE8" s="2" t="n"/>
       <c r="AF8" s="2" t="n"/>
@@ -2355,39 +2310,15 @@
       <c r="AK8" s="2" t="n"/>
       <c r="AL8" s="2" t="n"/>
       <c r="AM8" s="2" t="n"/>
-      <c r="AN8" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="AN8" s="2" t="n"/>
       <c r="AO8" s="2" t="n"/>
       <c r="AP8" s="2" t="n"/>
       <c r="AQ8" s="2" t="n"/>
-      <c r="AR8" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="AS8" s="2" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="AT8" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AU8" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AV8" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="AR8" s="2" t="n"/>
+      <c r="AS8" s="2" t="n"/>
+      <c r="AT8" s="2" t="n"/>
+      <c r="AU8" s="2" t="n"/>
+      <c r="AV8" s="2" t="n"/>
       <c r="AW8" s="2" t="n"/>
       <c r="AX8" s="2" t="n"/>
       <c r="AY8" s="2" t="n"/>
@@ -2441,22 +2372,11 @@
       <c r="CU8" s="2" t="n"/>
       <c r="CV8" s="2" t="n"/>
       <c r="CW8" s="2" t="n"/>
-      <c r="CX8" s="2" t="n"/>
-      <c r="CY8" s="2" t="n"/>
-      <c r="CZ8" s="2" t="n"/>
-      <c r="DA8" s="2" t="n"/>
-      <c r="DB8" s="2" t="n"/>
-      <c r="DC8" s="2" t="n"/>
-      <c r="DD8" s="2" t="n"/>
-      <c r="DE8" s="2" t="n"/>
-      <c r="DF8" s="2" t="n"/>
-      <c r="DG8" s="2" t="n"/>
-      <c r="DH8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>600-P-01</t>
+          <t>200-P-01B</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -2465,69 +2385,115 @@
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Bomba centrifuga horizontal</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Bomba de lodos biológicos</t>
+          <t>Recirculación de agua clarificada para microburbuja</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Trasiego de lodos desde 200-PS-01 hacia 600-TK-02</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Discontinua</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Lodos biológicos</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n"/>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6 a 9</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Neumática</t>
-        </is>
-      </c>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n"/>
-      <c r="R9" s="2" t="n"/>
-      <c r="S9" s="2" t="n"/>
-      <c r="T9" s="2" t="n"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Cuerpo AISI 304 
+Impulsor AISI 304
+Carcasa AISI304</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Centrifuga horizontal</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>Cuerpo: Polipropileno
-Diafragma en santopreno</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>WILDEN P1</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="n"/>
-      <c r="X9" s="2" t="n"/>
-      <c r="Y9" s="2" t="n"/>
-      <c r="Z9" s="2" t="n"/>
-      <c r="AA9" s="2" t="n"/>
-      <c r="AB9" s="2" t="n"/>
-      <c r="AC9" s="2" t="n"/>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>0.8627450980392157</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>Succión: 2½″ NPT hembra
+Descarga: 2″ NPT hembra</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>Directo-en-línea (DOL)</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>2CDX 70/306</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="n"/>
       <c r="AE9" s="2" t="n"/>
       <c r="AF9" s="2" t="n"/>
@@ -2543,57 +2509,19 @@
       <c r="AP9" s="2" t="n"/>
       <c r="AQ9" s="2" t="n"/>
       <c r="AR9" s="2" t="n"/>
-      <c r="AS9" s="2" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
+      <c r="AS9" s="2" t="n"/>
       <c r="AT9" s="2" t="n"/>
       <c r="AU9" s="2" t="n"/>
       <c r="AV9" s="2" t="n"/>
-      <c r="AW9" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="AX9" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="AY9" s="2" t="inlineStr">
-        <is>
-          <t>3180</t>
-        </is>
-      </c>
-      <c r="AZ9" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="BA9" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="BB9" s="2" t="inlineStr">
-        <is>
-          <t>5.18 dry</t>
-        </is>
-      </c>
-      <c r="BC9" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BD9" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BE9" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
+      <c r="AW9" s="2" t="n"/>
+      <c r="AX9" s="2" t="n"/>
+      <c r="AY9" s="2" t="n"/>
+      <c r="AZ9" s="2" t="n"/>
+      <c r="BA9" s="2" t="n"/>
+      <c r="BB9" s="2" t="n"/>
+      <c r="BC9" s="2" t="n"/>
+      <c r="BD9" s="2" t="n"/>
+      <c r="BE9" s="2" t="n"/>
       <c r="BF9" s="2" t="n"/>
       <c r="BG9" s="2" t="n"/>
       <c r="BH9" s="2" t="n"/>
@@ -2638,22 +2566,11 @@
       <c r="CU9" s="2" t="n"/>
       <c r="CV9" s="2" t="n"/>
       <c r="CW9" s="2" t="n"/>
-      <c r="CX9" s="2" t="n"/>
-      <c r="CY9" s="2" t="n"/>
-      <c r="CZ9" s="2" t="n"/>
-      <c r="DA9" s="2" t="n"/>
-      <c r="DB9" s="2" t="n"/>
-      <c r="DC9" s="2" t="n"/>
-      <c r="DD9" s="2" t="n"/>
-      <c r="DE9" s="2" t="n"/>
-      <c r="DF9" s="2" t="n"/>
-      <c r="DG9" s="2" t="n"/>
-      <c r="DH9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>600-P-02</t>
+          <t>400-MX-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2662,62 +2579,45 @@
         </is>
       </c>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Aire</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Bomba de lodos biológicos</t>
+          <t>Difusor de aire para los reactores biológicos</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Trasiego de lodos biológicos desde 600-TK-02 hacia filtro prensa 600-SD-01</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Discontinua</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Lodos biológicos</t>
-        </is>
-      </c>
+          <t>Aire</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6 a 9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Neumática</t>
-        </is>
-      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="2" t="n"/>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>Cuerpo: Polipropileno
-Diafragma en santopreno</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>WILDEN P1</t>
-        </is>
-      </c>
+      <c r="U10" s="2" t="n"/>
+      <c r="V10" s="2" t="n"/>
       <c r="W10" s="2" t="n"/>
       <c r="X10" s="2" t="n"/>
       <c r="Y10" s="2" t="n"/>
@@ -2725,11 +2625,31 @@
       <c r="AA10" s="2" t="n"/>
       <c r="AB10" s="2" t="n"/>
       <c r="AC10" s="2" t="n"/>
-      <c r="AD10" s="2" t="n"/>
-      <c r="AE10" s="2" t="n"/>
-      <c r="AF10" s="2" t="n"/>
-      <c r="AG10" s="2" t="n"/>
-      <c r="AH10" s="2" t="n"/>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>Axial</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>Lateral 1"</t>
+        </is>
+      </c>
       <c r="AI10" s="2" t="n"/>
       <c r="AJ10" s="2" t="n"/>
       <c r="AK10" s="2" t="n"/>
@@ -2740,59 +2660,21 @@
       <c r="AP10" s="2" t="n"/>
       <c r="AQ10" s="2" t="n"/>
       <c r="AR10" s="2" t="n"/>
-      <c r="AS10" s="2" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
+      <c r="AS10" s="2" t="n"/>
       <c r="AT10" s="2" t="n"/>
       <c r="AU10" s="2" t="n"/>
       <c r="AV10" s="2" t="n"/>
       <c r="AW10" s="2" t="n"/>
       <c r="AX10" s="2" t="n"/>
-      <c r="AY10" s="2" t="inlineStr">
-        <is>
-          <t>3180</t>
-        </is>
-      </c>
-      <c r="AZ10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="BA10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="BB10" s="2" t="inlineStr">
-        <is>
-          <t>5.18 dry</t>
-        </is>
-      </c>
-      <c r="BC10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BD10" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BE10" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="BF10" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="BG10" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
+      <c r="AY10" s="2" t="n"/>
+      <c r="AZ10" s="2" t="n"/>
+      <c r="BA10" s="2" t="n"/>
+      <c r="BB10" s="2" t="n"/>
+      <c r="BC10" s="2" t="n"/>
+      <c r="BD10" s="2" t="n"/>
+      <c r="BE10" s="2" t="n"/>
+      <c r="BF10" s="2" t="n"/>
+      <c r="BG10" s="2" t="n"/>
       <c r="BH10" s="2" t="n"/>
       <c r="BI10" s="2" t="n"/>
       <c r="BJ10" s="2" t="n"/>
@@ -2835,51 +2717,40 @@
       <c r="CU10" s="2" t="n"/>
       <c r="CV10" s="2" t="n"/>
       <c r="CW10" s="2" t="n"/>
-      <c r="CX10" s="2" t="n"/>
-      <c r="CY10" s="2" t="n"/>
-      <c r="CZ10" s="2" t="n"/>
-      <c r="DA10" s="2" t="n"/>
-      <c r="DB10" s="2" t="n"/>
-      <c r="DC10" s="2" t="n"/>
-      <c r="DD10" s="2" t="n"/>
-      <c r="DE10" s="2" t="n"/>
-      <c r="DF10" s="2" t="n"/>
-      <c r="DG10" s="2" t="n"/>
-      <c r="DH10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>800-TK-01</t>
+          <t>400-MX-02</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TANQUES</t>
+          <t>EQUIPOS</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Aire</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Tanque Coagulante</t>
+          <t>Difusor de aire para los reactores biológicos</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Almacenamiento y dosificación de coagulante</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Continuo</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Coagulante</t>
-        </is>
-      </c>
+          <t>Aire</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
@@ -2888,15 +2759,15 @@
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="2" t="n"/>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>Polietileno</t>
-        </is>
-      </c>
+      <c r="U11" s="2" t="n"/>
       <c r="V11" s="2" t="n"/>
       <c r="W11" s="2" t="n"/>
       <c r="X11" s="2" t="n"/>
@@ -2905,25 +2776,37 @@
       <c r="AA11" s="2" t="n"/>
       <c r="AB11" s="2" t="n"/>
       <c r="AC11" s="2" t="n"/>
-      <c r="AD11" s="2" t="n"/>
-      <c r="AE11" s="2" t="n"/>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
       <c r="AF11" s="2" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG11" s="2" t="n"/>
-      <c r="AH11" s="2" t="n"/>
+          <t>Axial</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="inlineStr">
+        <is>
+          <t>Lateral 1"</t>
+        </is>
+      </c>
       <c r="AI11" s="2" t="n"/>
       <c r="AJ11" s="2" t="n"/>
       <c r="AK11" s="2" t="n"/>
       <c r="AL11" s="2" t="n"/>
       <c r="AM11" s="2" t="n"/>
-      <c r="AN11" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="AN11" s="2" t="n"/>
       <c r="AO11" s="2" t="n"/>
       <c r="AP11" s="2" t="n"/>
       <c r="AQ11" s="2" t="n"/>
@@ -2931,11 +2814,7 @@
       <c r="AS11" s="2" t="n"/>
       <c r="AT11" s="2" t="n"/>
       <c r="AU11" s="2" t="n"/>
-      <c r="AV11" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+      <c r="AV11" s="2" t="n"/>
       <c r="AW11" s="2" t="n"/>
       <c r="AX11" s="2" t="n"/>
       <c r="AY11" s="2" t="n"/>
@@ -2947,26 +2826,10 @@
       <c r="BE11" s="2" t="n"/>
       <c r="BF11" s="2" t="n"/>
       <c r="BG11" s="2" t="n"/>
-      <c r="BH11" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="BI11" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="BJ11" s="2" t="inlineStr">
-        <is>
-          <t>Caneca</t>
-        </is>
-      </c>
-      <c r="BK11" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+      <c r="BH11" s="2" t="n"/>
+      <c r="BI11" s="2" t="n"/>
+      <c r="BJ11" s="2" t="n"/>
+      <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
@@ -3005,22 +2868,11 @@
       <c r="CU11" s="2" t="n"/>
       <c r="CV11" s="2" t="n"/>
       <c r="CW11" s="2" t="n"/>
-      <c r="CX11" s="2" t="n"/>
-      <c r="CY11" s="2" t="n"/>
-      <c r="CZ11" s="2" t="n"/>
-      <c r="DA11" s="2" t="n"/>
-      <c r="DB11" s="2" t="n"/>
-      <c r="DC11" s="2" t="n"/>
-      <c r="DD11" s="2" t="n"/>
-      <c r="DE11" s="2" t="n"/>
-      <c r="DF11" s="2" t="n"/>
-      <c r="DG11" s="2" t="n"/>
-      <c r="DH11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>800-P-01</t>
+          <t>400-MX-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3029,50 +2881,44 @@
         </is>
       </c>
       <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Aire</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Bomba dosificadora</t>
+          <t>Difusor de aire para los reactores biológicos</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Dosificación de coagulante en mezclador estático 200-MX-01</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Coagulante</t>
-        </is>
-      </c>
+          <t>Aire</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>Diafragma eléctrica</t>
-        </is>
-      </c>
+      <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="2" t="n"/>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>Cabezal de dosificación: cloruro de polivinilo (PVC) 
-Bola de válvula: Cerámica
- Junta de estanqueidad: PTFE</t>
-        </is>
-      </c>
+      <c r="U12" s="2" t="n"/>
       <c r="V12" s="2" t="n"/>
       <c r="W12" s="2" t="n"/>
       <c r="X12" s="2" t="n"/>
@@ -3081,22 +2927,34 @@
       <c r="AA12" s="2" t="n"/>
       <c r="AB12" s="2" t="n"/>
       <c r="AC12" s="2" t="n"/>
-      <c r="AD12" s="2" t="n"/>
-      <c r="AE12" s="2" t="n"/>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
       <c r="AF12" s="2" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG12" s="2" t="n"/>
-      <c r="AH12" s="2" t="n"/>
+          <t>Axial</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>Lateral 1"</t>
+        </is>
+      </c>
       <c r="AI12" s="2" t="n"/>
       <c r="AJ12" s="2" t="n"/>
-      <c r="AK12" s="2" t="inlineStr">
-        <is>
-          <t>GRUNDFOS  Modelo DDA 7.5-16 AR</t>
-        </is>
-      </c>
+      <c r="AK12" s="2" t="n"/>
       <c r="AL12" s="2" t="n"/>
       <c r="AM12" s="2" t="n"/>
       <c r="AN12" s="2" t="n"/>
@@ -3123,44 +2981,14 @@
       <c r="BI12" s="2" t="n"/>
       <c r="BJ12" s="2" t="n"/>
       <c r="BK12" s="2" t="n"/>
-      <c r="BL12" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="BM12" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="BN12" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="BO12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BP12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BQ12" s="2" t="inlineStr">
-        <is>
-          <t>IP65 / NEMA 4X</t>
-        </is>
-      </c>
-      <c r="BR12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="BS12" s="2" t="inlineStr">
-        <is>
-          <t>10 - 45</t>
-        </is>
-      </c>
+      <c r="BL12" s="2" t="n"/>
+      <c r="BM12" s="2" t="n"/>
+      <c r="BN12" s="2" t="n"/>
+      <c r="BO12" s="2" t="n"/>
+      <c r="BP12" s="2" t="n"/>
+      <c r="BQ12" s="2" t="n"/>
+      <c r="BR12" s="2" t="n"/>
+      <c r="BS12" s="2" t="n"/>
       <c r="BT12" s="2" t="n"/>
       <c r="BU12" s="2" t="n"/>
       <c r="BV12" s="2" t="n"/>
@@ -3191,51 +3019,40 @@
       <c r="CU12" s="2" t="n"/>
       <c r="CV12" s="2" t="n"/>
       <c r="CW12" s="2" t="n"/>
-      <c r="CX12" s="2" t="n"/>
-      <c r="CY12" s="2" t="n"/>
-      <c r="CZ12" s="2" t="n"/>
-      <c r="DA12" s="2" t="n"/>
-      <c r="DB12" s="2" t="n"/>
-      <c r="DC12" s="2" t="n"/>
-      <c r="DD12" s="2" t="n"/>
-      <c r="DE12" s="2" t="n"/>
-      <c r="DF12" s="2" t="n"/>
-      <c r="DG12" s="2" t="n"/>
-      <c r="DH12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>801-TK-01</t>
+          <t>400-MX-04</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>TANQUES</t>
+          <t>EQUIPOS</t>
         </is>
       </c>
       <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Aire</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tanque de soda</t>
+          <t>Difusor de aire para los reactores biológicos</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Almacenamiento y dosificación de soda</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Continuo</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Soda</t>
-        </is>
-      </c>
+          <t>Aire</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
@@ -3244,15 +3061,15 @@
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="2" t="n"/>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>Polietileno</t>
-        </is>
-      </c>
+      <c r="U13" s="2" t="n"/>
       <c r="V13" s="2" t="n"/>
       <c r="W13" s="2" t="n"/>
       <c r="X13" s="2" t="n"/>
@@ -3261,25 +3078,37 @@
       <c r="AA13" s="2" t="n"/>
       <c r="AB13" s="2" t="n"/>
       <c r="AC13" s="2" t="n"/>
-      <c r="AD13" s="2" t="n"/>
-      <c r="AE13" s="2" t="n"/>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
       <c r="AF13" s="2" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG13" s="2" t="n"/>
-      <c r="AH13" s="2" t="n"/>
+          <t>Axial</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
+          <t>Lateral 1"</t>
+        </is>
+      </c>
       <c r="AI13" s="2" t="n"/>
       <c r="AJ13" s="2" t="n"/>
       <c r="AK13" s="2" t="n"/>
       <c r="AL13" s="2" t="n"/>
       <c r="AM13" s="2" t="n"/>
-      <c r="AN13" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="AN13" s="2" t="n"/>
       <c r="AO13" s="2" t="n"/>
       <c r="AP13" s="2" t="n"/>
       <c r="AQ13" s="2" t="n"/>
@@ -3287,11 +3116,7 @@
       <c r="AS13" s="2" t="n"/>
       <c r="AT13" s="2" t="n"/>
       <c r="AU13" s="2" t="n"/>
-      <c r="AV13" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+      <c r="AV13" s="2" t="n"/>
       <c r="AW13" s="2" t="n"/>
       <c r="AX13" s="2" t="n"/>
       <c r="AY13" s="2" t="n"/>
@@ -3305,33 +3130,17 @@
       <c r="BG13" s="2" t="n"/>
       <c r="BH13" s="2" t="n"/>
       <c r="BI13" s="2" t="n"/>
-      <c r="BJ13" s="2" t="inlineStr">
-        <is>
-          <t>Caneca</t>
-        </is>
-      </c>
-      <c r="BK13" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+      <c r="BJ13" s="2" t="n"/>
+      <c r="BK13" s="2" t="n"/>
       <c r="BL13" s="2" t="n"/>
       <c r="BM13" s="2" t="n"/>
-      <c r="BN13" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
+      <c r="BN13" s="2" t="n"/>
       <c r="BO13" s="2" t="n"/>
       <c r="BP13" s="2" t="n"/>
       <c r="BQ13" s="2" t="n"/>
       <c r="BR13" s="2" t="n"/>
       <c r="BS13" s="2" t="n"/>
-      <c r="BT13" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
+      <c r="BT13" s="2" t="n"/>
       <c r="BU13" s="2" t="n"/>
       <c r="BV13" s="2" t="n"/>
       <c r="BW13" s="2" t="n"/>
@@ -3361,22 +3170,11 @@
       <c r="CU13" s="2" t="n"/>
       <c r="CV13" s="2" t="n"/>
       <c r="CW13" s="2" t="n"/>
-      <c r="CX13" s="2" t="n"/>
-      <c r="CY13" s="2" t="n"/>
-      <c r="CZ13" s="2" t="n"/>
-      <c r="DA13" s="2" t="n"/>
-      <c r="DB13" s="2" t="n"/>
-      <c r="DC13" s="2" t="n"/>
-      <c r="DD13" s="2" t="n"/>
-      <c r="DE13" s="2" t="n"/>
-      <c r="DF13" s="2" t="n"/>
-      <c r="DG13" s="2" t="n"/>
-      <c r="DH13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>801-P-01A</t>
+          <t>400-M-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3385,50 +3183,48 @@
         </is>
       </c>
       <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Biocarrier</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Bomba dosificadora</t>
+          <t>Soporte de microorganismos para remoción de materia orgánica en los reactores biológicos</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Dosificación de soda</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>soda cáustica</t>
-        </is>
-      </c>
+          <t>Agua residual no domestica</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>Diafragma eléctrica</t>
-        </is>
-      </c>
+      <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Polietileno</t>
+        </is>
+      </c>
       <c r="R14" s="2" t="n"/>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="2" t="n"/>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>Cabezal de dosificación: cloruro de polivinilo (PVC) 
-Bola de válvula: Cerámica
- Junta de estanqueidad: PTFE</t>
-        </is>
-      </c>
+      <c r="U14" s="2" t="n"/>
       <c r="V14" s="2" t="n"/>
       <c r="W14" s="2" t="n"/>
       <c r="X14" s="2" t="n"/>
@@ -3439,23 +3235,39 @@
       <c r="AC14" s="2" t="n"/>
       <c r="AD14" s="2" t="n"/>
       <c r="AE14" s="2" t="n"/>
-      <c r="AF14" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="AF14" s="2" t="n"/>
       <c r="AG14" s="2" t="n"/>
       <c r="AH14" s="2" t="n"/>
-      <c r="AI14" s="2" t="n"/>
-      <c r="AJ14" s="2" t="n"/>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>Mutag BioChip30</t>
+        </is>
+      </c>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>Redondo, paraboloide</t>
+        </is>
+      </c>
       <c r="AK14" s="2" t="inlineStr">
         <is>
-          <t>GRUNDFOS Modelo:  DDC 15-4AR</t>
-        </is>
-      </c>
-      <c r="AL14" s="2" t="n"/>
-      <c r="AM14" s="2" t="n"/>
-      <c r="AN14" s="2" t="n"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AL14" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AM14" s="2" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="AN14" s="2" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
       <c r="AO14" s="2" t="n"/>
       <c r="AP14" s="2" t="n"/>
       <c r="AQ14" s="2" t="n"/>
@@ -3481,45 +3293,15 @@
       <c r="BK14" s="2" t="n"/>
       <c r="BL14" s="2" t="n"/>
       <c r="BM14" s="2" t="n"/>
-      <c r="BN14" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="BO14" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BP14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BQ14" s="2" t="inlineStr">
-        <is>
-          <t>IP65 / NEMA 4X</t>
-        </is>
-      </c>
-      <c r="BR14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="BS14" s="2" t="inlineStr">
-        <is>
-          <t>10 - 45</t>
-        </is>
-      </c>
+      <c r="BN14" s="2" t="n"/>
+      <c r="BO14" s="2" t="n"/>
+      <c r="BP14" s="2" t="n"/>
+      <c r="BQ14" s="2" t="n"/>
+      <c r="BR14" s="2" t="n"/>
+      <c r="BS14" s="2" t="n"/>
       <c r="BT14" s="2" t="n"/>
-      <c r="BU14" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="BV14" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
+      <c r="BU14" s="2" t="n"/>
+      <c r="BV14" s="2" t="n"/>
       <c r="BW14" s="2" t="n"/>
       <c r="BX14" s="2" t="n"/>
       <c r="BY14" s="2" t="n"/>
@@ -3547,22 +3329,11 @@
       <c r="CU14" s="2" t="n"/>
       <c r="CV14" s="2" t="n"/>
       <c r="CW14" s="2" t="n"/>
-      <c r="CX14" s="2" t="n"/>
-      <c r="CY14" s="2" t="n"/>
-      <c r="CZ14" s="2" t="n"/>
-      <c r="DA14" s="2" t="n"/>
-      <c r="DB14" s="2" t="n"/>
-      <c r="DC14" s="2" t="n"/>
-      <c r="DD14" s="2" t="n"/>
-      <c r="DE14" s="2" t="n"/>
-      <c r="DF14" s="2" t="n"/>
-      <c r="DG14" s="2" t="n"/>
-      <c r="DH14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>801-P-01B</t>
+          <t>400-M-02</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -3571,50 +3342,48 @@
         </is>
       </c>
       <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Biocarrier</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Bomba dosificadora (standby)</t>
+          <t>Soporte de microorganismos para remoción de materia orgánica en los reactores biológicos</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Dosificación de soda</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>soda cáustica</t>
-        </is>
-      </c>
+          <t>Agua residual no domestica</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>Diafragma eléctrica</t>
-        </is>
-      </c>
+      <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Polietileno</t>
+        </is>
+      </c>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="n"/>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>Cabezal de dosificación: cloruro de polivinilo (PVC) 
-Bola de válvula: Cerámica
- Junta de estanqueidad: PTFE</t>
-        </is>
-      </c>
+      <c r="U15" s="2" t="n"/>
       <c r="V15" s="2" t="n"/>
       <c r="W15" s="2" t="n"/>
       <c r="X15" s="2" t="n"/>
@@ -3625,23 +3394,39 @@
       <c r="AC15" s="2" t="n"/>
       <c r="AD15" s="2" t="n"/>
       <c r="AE15" s="2" t="n"/>
-      <c r="AF15" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="AF15" s="2" t="n"/>
       <c r="AG15" s="2" t="n"/>
       <c r="AH15" s="2" t="n"/>
-      <c r="AI15" s="2" t="n"/>
-      <c r="AJ15" s="2" t="n"/>
+      <c r="AI15" s="2" t="inlineStr">
+        <is>
+          <t>Mutag BioChip30</t>
+        </is>
+      </c>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>Redondo, paraboloide</t>
+        </is>
+      </c>
       <c r="AK15" s="2" t="inlineStr">
         <is>
-          <t>GRUNDFOS Modelo:  DDC 15-4AR</t>
-        </is>
-      </c>
-      <c r="AL15" s="2" t="n"/>
-      <c r="AM15" s="2" t="n"/>
-      <c r="AN15" s="2" t="n"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AL15" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AM15" s="2" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="AN15" s="2" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
       <c r="AO15" s="2" t="n"/>
       <c r="AP15" s="2" t="n"/>
       <c r="AQ15" s="2" t="n"/>
@@ -3667,46 +3452,16 @@
       <c r="BK15" s="2" t="n"/>
       <c r="BL15" s="2" t="n"/>
       <c r="BM15" s="2" t="n"/>
-      <c r="BN15" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="BO15" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BP15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BQ15" s="2" t="inlineStr">
-        <is>
-          <t>IP65 / NEMA 4X</t>
-        </is>
-      </c>
-      <c r="BR15" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="BS15" s="2" t="inlineStr">
-        <is>
-          <t>10 - 45</t>
-        </is>
-      </c>
+      <c r="BN15" s="2" t="n"/>
+      <c r="BO15" s="2" t="n"/>
+      <c r="BP15" s="2" t="n"/>
+      <c r="BQ15" s="2" t="n"/>
+      <c r="BR15" s="2" t="n"/>
+      <c r="BS15" s="2" t="n"/>
       <c r="BT15" s="2" t="n"/>
-      <c r="BU15" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
+      <c r="BU15" s="2" t="n"/>
       <c r="BV15" s="2" t="n"/>
-      <c r="BW15" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
+      <c r="BW15" s="2" t="n"/>
       <c r="BX15" s="2" t="n"/>
       <c r="BY15" s="2" t="n"/>
       <c r="BZ15" s="2" t="n"/>
@@ -3733,76 +3488,61 @@
       <c r="CU15" s="2" t="n"/>
       <c r="CV15" s="2" t="n"/>
       <c r="CW15" s="2" t="n"/>
-      <c r="CX15" s="2" t="n"/>
-      <c r="CY15" s="2" t="n"/>
-      <c r="CZ15" s="2" t="n"/>
-      <c r="DA15" s="2" t="n"/>
-      <c r="DB15" s="2" t="n"/>
-      <c r="DC15" s="2" t="n"/>
-      <c r="DD15" s="2" t="n"/>
-      <c r="DE15" s="2" t="n"/>
-      <c r="DF15" s="2" t="n"/>
-      <c r="DG15" s="2" t="n"/>
-      <c r="DH15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>802-TK-01</t>
+          <t>400-M-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TANQUES</t>
+          <t>EQUIPOS</t>
         </is>
       </c>
       <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Biocarrier</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tanque de floculante</t>
+          <t>Soporte de microorganismos para remoción de materia orgánica en los reactores biológicos</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Preparación, almacenamiento y dosificación de Polímero Floculante</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Floculante</t>
-        </is>
-      </c>
+          <t>Agua residual no domestica</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5.0-9.0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Polietileno</t>
+        </is>
+      </c>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="n"/>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>POLIETILENO</t>
-        </is>
-      </c>
+      <c r="U16" s="2" t="n"/>
       <c r="V16" s="2" t="n"/>
       <c r="W16" s="2" t="n"/>
       <c r="X16" s="2" t="n"/>
@@ -3816,14 +3556,34 @@
       <c r="AF16" s="2" t="n"/>
       <c r="AG16" s="2" t="n"/>
       <c r="AH16" s="2" t="n"/>
-      <c r="AI16" s="2" t="n"/>
-      <c r="AJ16" s="2" t="n"/>
-      <c r="AK16" s="2" t="n"/>
-      <c r="AL16" s="2" t="n"/>
-      <c r="AM16" s="2" t="n"/>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>Mutag BioChip30</t>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>Redondo, paraboloide</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AL16" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AM16" s="2" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="AO16" s="2" t="n"/>
@@ -3831,21 +3591,9 @@
       <c r="AQ16" s="2" t="n"/>
       <c r="AR16" s="2" t="n"/>
       <c r="AS16" s="2" t="n"/>
-      <c r="AT16" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AU16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AV16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="AT16" s="2" t="n"/>
+      <c r="AU16" s="2" t="n"/>
+      <c r="AV16" s="2" t="n"/>
       <c r="AW16" s="2" t="n"/>
       <c r="AX16" s="2" t="n"/>
       <c r="AY16" s="2" t="n"/>
@@ -3863,11 +3611,7 @@
       <c r="BK16" s="2" t="n"/>
       <c r="BL16" s="2" t="n"/>
       <c r="BM16" s="2" t="n"/>
-      <c r="BN16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BN16" s="2" t="n"/>
       <c r="BO16" s="2" t="n"/>
       <c r="BP16" s="2" t="n"/>
       <c r="BQ16" s="2" t="n"/>
@@ -3877,11 +3621,7 @@
       <c r="BU16" s="2" t="n"/>
       <c r="BV16" s="2" t="n"/>
       <c r="BW16" s="2" t="n"/>
-      <c r="BX16" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
+      <c r="BX16" s="2" t="n"/>
       <c r="BY16" s="2" t="n"/>
       <c r="BZ16" s="2" t="n"/>
       <c r="CA16" s="2" t="n"/>
@@ -3907,22 +3647,11 @@
       <c r="CU16" s="2" t="n"/>
       <c r="CV16" s="2" t="n"/>
       <c r="CW16" s="2" t="n"/>
-      <c r="CX16" s="2" t="n"/>
-      <c r="CY16" s="2" t="n"/>
-      <c r="CZ16" s="2" t="n"/>
-      <c r="DA16" s="2" t="n"/>
-      <c r="DB16" s="2" t="n"/>
-      <c r="DC16" s="2" t="n"/>
-      <c r="DD16" s="2" t="n"/>
-      <c r="DE16" s="2" t="n"/>
-      <c r="DF16" s="2" t="n"/>
-      <c r="DG16" s="2" t="n"/>
-      <c r="DH16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>802-P-01A</t>
+          <t>400-M-04</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -3931,54 +3660,49 @@
         </is>
       </c>
       <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Biocarrier</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Bomba dosificadora</t>
+          <t>Soporte de microorganismos para remoción de materia orgánica en los reactores biológicos</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Dosificación de floculante en mezclador estático 200-MX-01</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Floculante</t>
-        </is>
-      </c>
+          <t>Agua residual no domestica</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>Neumática</t>
-        </is>
-      </c>
+      <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="n"/>
-      <c r="Q17" s="2" t="n"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Polietileno</t>
+        </is>
+      </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="2" t="n"/>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>Cuerpo: Polipropileno
-Diafragma en teflon</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>GRACO HUSKY 205</t>
-        </is>
-      </c>
+      <c r="U17" s="2" t="n"/>
+      <c r="V17" s="2" t="n"/>
       <c r="W17" s="2" t="n"/>
       <c r="X17" s="2" t="n"/>
       <c r="Y17" s="2" t="n"/>
@@ -3988,19 +3712,39 @@
       <c r="AC17" s="2" t="n"/>
       <c r="AD17" s="2" t="n"/>
       <c r="AE17" s="2" t="n"/>
-      <c r="AF17" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="AF17" s="2" t="n"/>
       <c r="AG17" s="2" t="n"/>
       <c r="AH17" s="2" t="n"/>
-      <c r="AI17" s="2" t="n"/>
-      <c r="AJ17" s="2" t="n"/>
-      <c r="AK17" s="2" t="n"/>
-      <c r="AL17" s="2" t="n"/>
-      <c r="AM17" s="2" t="n"/>
-      <c r="AN17" s="2" t="n"/>
+      <c r="AI17" s="2" t="inlineStr">
+        <is>
+          <t>Mutag BioChip30</t>
+        </is>
+      </c>
+      <c r="AJ17" s="2" t="inlineStr">
+        <is>
+          <t>Redondo, paraboloide</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AL17" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AM17" s="2" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="AN17" s="2" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
       <c r="AO17" s="2" t="n"/>
       <c r="AP17" s="2" t="n"/>
       <c r="AQ17" s="2" t="n"/>
@@ -4011,41 +3755,13 @@
       <c r="AV17" s="2" t="n"/>
       <c r="AW17" s="2" t="n"/>
       <c r="AX17" s="2" t="n"/>
-      <c r="AY17" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AZ17" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="BA17" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="BB17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BC17" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BD17" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BE17" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
+      <c r="AY17" s="2" t="n"/>
+      <c r="AZ17" s="2" t="n"/>
+      <c r="BA17" s="2" t="n"/>
+      <c r="BB17" s="2" t="n"/>
+      <c r="BC17" s="2" t="n"/>
+      <c r="BD17" s="2" t="n"/>
+      <c r="BE17" s="2" t="n"/>
       <c r="BF17" s="2" t="n"/>
       <c r="BG17" s="2" t="n"/>
       <c r="BH17" s="2" t="n"/>
@@ -4054,11 +3770,7 @@
       <c r="BK17" s="2" t="n"/>
       <c r="BL17" s="2" t="n"/>
       <c r="BM17" s="2" t="n"/>
-      <c r="BN17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BN17" s="2" t="n"/>
       <c r="BO17" s="2" t="n"/>
       <c r="BP17" s="2" t="n"/>
       <c r="BQ17" s="2" t="n"/>
@@ -4069,16 +3781,8 @@
       <c r="BV17" s="2" t="n"/>
       <c r="BW17" s="2" t="n"/>
       <c r="BX17" s="2" t="n"/>
-      <c r="BY17" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="BZ17" s="2" t="inlineStr">
-        <is>
-          <t>75.5</t>
-        </is>
-      </c>
+      <c r="BY17" s="2" t="n"/>
+      <c r="BZ17" s="2" t="n"/>
       <c r="CA17" s="2" t="n"/>
       <c r="CB17" s="2" t="n"/>
       <c r="CC17" s="2" t="n"/>
@@ -4102,78 +3806,94 @@
       <c r="CU17" s="2" t="n"/>
       <c r="CV17" s="2" t="n"/>
       <c r="CW17" s="2" t="n"/>
-      <c r="CX17" s="2" t="n"/>
-      <c r="CY17" s="2" t="n"/>
-      <c r="CZ17" s="2" t="n"/>
-      <c r="DA17" s="2" t="n"/>
-      <c r="DB17" s="2" t="n"/>
-      <c r="DC17" s="2" t="n"/>
-      <c r="DD17" s="2" t="n"/>
-      <c r="DE17" s="2" t="n"/>
-      <c r="DF17" s="2" t="n"/>
-      <c r="DG17" s="2" t="n"/>
-      <c r="DH17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>802-P-01B</t>
+          <t>400-R-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>EQUIPOS</t>
+          <t>TANQUES</t>
         </is>
       </c>
       <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Reactores biológicos</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Bomba dosificadora (Standby)</t>
+          <t>Reacción biológica</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Dosificación de floculante en mezclador estático 200-MX-01</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Floculante</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Cilíndrico Vertical con Fondo Plano</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Neumática</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n"/>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>PRFV</t>
+        </is>
+      </c>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="2" t="n"/>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>Cuerpo: Polipropileno
-Diafragma en teflon</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>GRACO HUSKY 205</t>
-        </is>
-      </c>
+      <c r="U18" s="2" t="n"/>
+      <c r="V18" s="2" t="n"/>
       <c r="W18" s="2" t="n"/>
       <c r="X18" s="2" t="n"/>
       <c r="Y18" s="2" t="n"/>
@@ -4183,11 +3903,7 @@
       <c r="AC18" s="2" t="n"/>
       <c r="AD18" s="2" t="n"/>
       <c r="AE18" s="2" t="n"/>
-      <c r="AF18" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="AF18" s="2" t="n"/>
       <c r="AG18" s="2" t="n"/>
       <c r="AH18" s="2" t="n"/>
       <c r="AI18" s="2" t="n"/>
@@ -4206,41 +3922,13 @@
       <c r="AV18" s="2" t="n"/>
       <c r="AW18" s="2" t="n"/>
       <c r="AX18" s="2" t="n"/>
-      <c r="AY18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AZ18" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="BA18" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="BB18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BC18" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BD18" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="BE18" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
+      <c r="AY18" s="2" t="n"/>
+      <c r="AZ18" s="2" t="n"/>
+      <c r="BA18" s="2" t="n"/>
+      <c r="BB18" s="2" t="n"/>
+      <c r="BC18" s="2" t="n"/>
+      <c r="BD18" s="2" t="n"/>
+      <c r="BE18" s="2" t="n"/>
       <c r="BF18" s="2" t="n"/>
       <c r="BG18" s="2" t="n"/>
       <c r="BH18" s="2" t="n"/>
@@ -4249,11 +3937,7 @@
       <c r="BK18" s="2" t="n"/>
       <c r="BL18" s="2" t="n"/>
       <c r="BM18" s="2" t="n"/>
-      <c r="BN18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BN18" s="2" t="n"/>
       <c r="BO18" s="2" t="n"/>
       <c r="BP18" s="2" t="n"/>
       <c r="BQ18" s="2" t="n"/>
@@ -4264,16 +3948,8 @@
       <c r="BV18" s="2" t="n"/>
       <c r="BW18" s="2" t="n"/>
       <c r="BX18" s="2" t="n"/>
-      <c r="BY18" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="BZ18" s="2" t="inlineStr">
-        <is>
-          <t>75.5</t>
-        </is>
-      </c>
+      <c r="BY18" s="2" t="n"/>
+      <c r="BZ18" s="2" t="n"/>
       <c r="CA18" s="2" t="n"/>
       <c r="CB18" s="2" t="n"/>
       <c r="CC18" s="2" t="n"/>
@@ -4297,22 +3973,11 @@
       <c r="CU18" s="2" t="n"/>
       <c r="CV18" s="2" t="n"/>
       <c r="CW18" s="2" t="n"/>
-      <c r="CX18" s="2" t="n"/>
-      <c r="CY18" s="2" t="n"/>
-      <c r="CZ18" s="2" t="n"/>
-      <c r="DA18" s="2" t="n"/>
-      <c r="DB18" s="2" t="n"/>
-      <c r="DC18" s="2" t="n"/>
-      <c r="DD18" s="2" t="n"/>
-      <c r="DE18" s="2" t="n"/>
-      <c r="DF18" s="2" t="n"/>
-      <c r="DG18" s="2" t="n"/>
-      <c r="DH18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>803-TK-01</t>
+          <t>400-R-02</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -4321,52 +3986,80 @@
         </is>
       </c>
       <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Reactores biológicos</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Tanque de deshidratante</t>
+          <t>Reacción biológica</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Preparación, almacenamiento y dosificación de Polímero deshidratante</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Discontinua</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Deshidratante</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n"/>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5.0-9.0</t>
+          <t>&lt;30</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n"/>
+          <t>Cilíndrico Vertical con Fondo Plano</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>PRFV</t>
+        </is>
+      </c>
       <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="2" t="n"/>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>POLIETILENO</t>
-        </is>
-      </c>
+      <c r="U19" s="2" t="n"/>
       <c r="V19" s="2" t="n"/>
       <c r="W19" s="2" t="n"/>
       <c r="X19" s="2" t="n"/>
@@ -4385,11 +4078,7 @@
       <c r="AK19" s="2" t="n"/>
       <c r="AL19" s="2" t="n"/>
       <c r="AM19" s="2" t="n"/>
-      <c r="AN19" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
+      <c r="AN19" s="2" t="n"/>
       <c r="AO19" s="2" t="n"/>
       <c r="AP19" s="2" t="n"/>
       <c r="AQ19" s="2" t="n"/>
@@ -4397,11 +4086,7 @@
       <c r="AS19" s="2" t="n"/>
       <c r="AT19" s="2" t="n"/>
       <c r="AU19" s="2" t="n"/>
-      <c r="AV19" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
+      <c r="AV19" s="2" t="n"/>
       <c r="AW19" s="2" t="n"/>
       <c r="AX19" s="2" t="n"/>
       <c r="AY19" s="2" t="n"/>
@@ -4419,11 +4104,7 @@
       <c r="BK19" s="2" t="n"/>
       <c r="BL19" s="2" t="n"/>
       <c r="BM19" s="2" t="n"/>
-      <c r="BN19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BN19" s="2" t="n"/>
       <c r="BO19" s="2" t="n"/>
       <c r="BP19" s="2" t="n"/>
       <c r="BQ19" s="2" t="n"/>
@@ -4436,16 +4117,8 @@
       <c r="BX19" s="2" t="n"/>
       <c r="BY19" s="2" t="n"/>
       <c r="BZ19" s="2" t="n"/>
-      <c r="CA19" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="CB19" s="2" t="inlineStr">
-        <is>
-          <t>58.5</t>
-        </is>
-      </c>
+      <c r="CA19" s="2" t="n"/>
+      <c r="CB19" s="2" t="n"/>
       <c r="CC19" s="2" t="n"/>
       <c r="CD19" s="2" t="n"/>
       <c r="CE19" s="2" t="n"/>
@@ -4467,78 +4140,94 @@
       <c r="CU19" s="2" t="n"/>
       <c r="CV19" s="2" t="n"/>
       <c r="CW19" s="2" t="n"/>
-      <c r="CX19" s="2" t="n"/>
-      <c r="CY19" s="2" t="n"/>
-      <c r="CZ19" s="2" t="n"/>
-      <c r="DA19" s="2" t="n"/>
-      <c r="DB19" s="2" t="n"/>
-      <c r="DC19" s="2" t="n"/>
-      <c r="DD19" s="2" t="n"/>
-      <c r="DE19" s="2" t="n"/>
-      <c r="DF19" s="2" t="n"/>
-      <c r="DG19" s="2" t="n"/>
-      <c r="DH19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>803-P-01</t>
+          <t>400-R-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>EQUIPOS</t>
+          <t>TANQUES</t>
         </is>
       </c>
       <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Reactores biológicos</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Bomba dosificadora</t>
+          <t>Reacción biológica</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Dosificación de deshidratante en tanque de lodos 600-TK-02</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Deshidrante</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Cilíndrico Vertical con Fondo Plano</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Neumática</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="n"/>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>PRFV</t>
+        </is>
+      </c>
       <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="2" t="n"/>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>Cuerpo: Polipropileno
-Diafragma en teflon</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>WILDEN P25</t>
-        </is>
-      </c>
+      <c r="U20" s="2" t="n"/>
+      <c r="V20" s="2" t="n"/>
       <c r="W20" s="2" t="n"/>
       <c r="X20" s="2" t="n"/>
       <c r="Y20" s="2" t="n"/>
@@ -4548,11 +4237,7 @@
       <c r="AC20" s="2" t="n"/>
       <c r="AD20" s="2" t="n"/>
       <c r="AE20" s="2" t="n"/>
-      <c r="AF20" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="AF20" s="2" t="n"/>
       <c r="AG20" s="2" t="n"/>
       <c r="AH20" s="2" t="n"/>
       <c r="AI20" s="2" t="n"/>
@@ -4571,41 +4256,13 @@
       <c r="AV20" s="2" t="n"/>
       <c r="AW20" s="2" t="n"/>
       <c r="AX20" s="2" t="n"/>
-      <c r="AY20" s="2" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
-      </c>
-      <c r="AZ20" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="BA20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BB20" s="2" t="inlineStr">
-        <is>
-          <t>3 dry</t>
-        </is>
-      </c>
-      <c r="BC20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD20" s="2" t="inlineStr">
-        <is>
-          <t>0.125</t>
-        </is>
-      </c>
-      <c r="BE20" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
+      <c r="AY20" s="2" t="n"/>
+      <c r="AZ20" s="2" t="n"/>
+      <c r="BA20" s="2" t="n"/>
+      <c r="BB20" s="2" t="n"/>
+      <c r="BC20" s="2" t="n"/>
+      <c r="BD20" s="2" t="n"/>
+      <c r="BE20" s="2" t="n"/>
       <c r="BF20" s="2" t="n"/>
       <c r="BG20" s="2" t="n"/>
       <c r="BH20" s="2" t="n"/>
@@ -4614,11 +4271,7 @@
       <c r="BK20" s="2" t="n"/>
       <c r="BL20" s="2" t="n"/>
       <c r="BM20" s="2" t="n"/>
-      <c r="BN20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BN20" s="2" t="n"/>
       <c r="BO20" s="2" t="n"/>
       <c r="BP20" s="2" t="n"/>
       <c r="BQ20" s="2" t="n"/>
@@ -4633,11 +4286,7 @@
       <c r="BZ20" s="2" t="n"/>
       <c r="CA20" s="2" t="n"/>
       <c r="CB20" s="2" t="n"/>
-      <c r="CC20" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
+      <c r="CC20" s="2" t="n"/>
       <c r="CD20" s="2" t="n"/>
       <c r="CE20" s="2" t="n"/>
       <c r="CF20" s="2" t="n"/>
@@ -4658,69 +4307,94 @@
       <c r="CU20" s="2" t="n"/>
       <c r="CV20" s="2" t="n"/>
       <c r="CW20" s="2" t="n"/>
-      <c r="CX20" s="2" t="n"/>
-      <c r="CY20" s="2" t="n"/>
-      <c r="CZ20" s="2" t="n"/>
-      <c r="DA20" s="2" t="n"/>
-      <c r="DB20" s="2" t="n"/>
-      <c r="DC20" s="2" t="n"/>
-      <c r="DD20" s="2" t="n"/>
-      <c r="DE20" s="2" t="n"/>
-      <c r="DF20" s="2" t="n"/>
-      <c r="DG20" s="2" t="n"/>
-      <c r="DH20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>600-M-01</t>
+          <t>400-R-04</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>EQUIPOS</t>
+          <t>TANQUES</t>
         </is>
       </c>
       <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Reactores biológicos</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Acondicionamiento de lodos</t>
+          <t>Reacción biológica</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Agitación de lodos</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Baches</t>
+          <t>Agua residual no domestica</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Lodos</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Cilíndrico Vertical con Fondo Plano</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>PRFV</t>
+        </is>
+      </c>
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="2" t="n"/>
       <c r="U21" s="2" t="n"/>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>SEW / FAF37 DRN90L4</t>
-        </is>
-      </c>
+      <c r="V21" s="2" t="n"/>
       <c r="W21" s="2" t="n"/>
       <c r="X21" s="2" t="n"/>
       <c r="Y21" s="2" t="n"/>
@@ -4730,11 +4404,7 @@
       <c r="AC21" s="2" t="n"/>
       <c r="AD21" s="2" t="n"/>
       <c r="AE21" s="2" t="n"/>
-      <c r="AF21" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="AF21" s="2" t="n"/>
       <c r="AG21" s="2" t="n"/>
       <c r="AH21" s="2" t="n"/>
       <c r="AI21" s="2" t="n"/>
@@ -4768,11 +4438,7 @@
       <c r="BK21" s="2" t="n"/>
       <c r="BL21" s="2" t="n"/>
       <c r="BM21" s="2" t="n"/>
-      <c r="BN21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BN21" s="2" t="n"/>
       <c r="BO21" s="2" t="n"/>
       <c r="BP21" s="2" t="n"/>
       <c r="BQ21" s="2" t="n"/>
@@ -4788,151 +4454,3458 @@
       <c r="CA21" s="2" t="n"/>
       <c r="CB21" s="2" t="n"/>
       <c r="CC21" s="2" t="n"/>
-      <c r="CD21" s="2" t="inlineStr">
-        <is>
-          <t>JCSA</t>
-        </is>
-      </c>
-      <c r="CE21" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="CF21" s="2" t="inlineStr">
-        <is>
-          <t>:1767 / 137</t>
-        </is>
-      </c>
-      <c r="CG21" s="2" t="inlineStr">
-        <is>
-          <t>12.87 / INFINITO</t>
-        </is>
-      </c>
-      <c r="CH21" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="CI21" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="CJ21" s="2" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="CK21" s="2" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="CL21" s="2" t="inlineStr">
-        <is>
-          <t>270 (T) / NORMAL</t>
-        </is>
-      </c>
-      <c r="CM21" s="2" t="inlineStr">
-        <is>
-          <t>CLP 220 ACEITE MINERAL / 1.25</t>
-        </is>
-      </c>
-      <c r="CN21" s="2" t="inlineStr">
-        <is>
-          <t>CAPA FINAL RAL 7031 (GRIS AZULADO)</t>
-        </is>
-      </c>
-      <c r="CO21" s="2" t="inlineStr">
-        <is>
-          <t>FAF37</t>
-        </is>
-      </c>
-      <c r="CP21" s="2" t="inlineStr">
-        <is>
-          <t>30 mm</t>
-        </is>
-      </c>
-      <c r="CQ21" s="2" t="inlineStr">
-        <is>
-          <t>CON BRIDA Y EJE HUECO</t>
-        </is>
-      </c>
-      <c r="CR21" s="2" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="CS21" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="CT21" s="2" t="inlineStr">
-        <is>
-          <t>ESTÁNDAR</t>
-        </is>
-      </c>
-      <c r="CU21" s="2" t="inlineStr">
-        <is>
-          <t>VÁLVULA DE VENTILACIÓN MONTADA EN LA BRIDA</t>
-        </is>
-      </c>
-      <c r="CV21" s="2" t="inlineStr">
-        <is>
-          <t>42001_95</t>
-        </is>
-      </c>
-      <c r="CW21" s="2" t="inlineStr">
-        <is>
-          <t>DRN90L4</t>
-        </is>
-      </c>
-      <c r="CX21" s="2" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="CY21" s="2" t="inlineStr">
+      <c r="CD21" s="2" t="n"/>
+      <c r="CE21" s="2" t="n"/>
+      <c r="CF21" s="2" t="n"/>
+      <c r="CG21" s="2" t="n"/>
+      <c r="CH21" s="2" t="n"/>
+      <c r="CI21" s="2" t="n"/>
+      <c r="CJ21" s="2" t="n"/>
+      <c r="CK21" s="2" t="n"/>
+      <c r="CL21" s="2" t="n"/>
+      <c r="CM21" s="2" t="n"/>
+      <c r="CN21" s="2" t="n"/>
+      <c r="CO21" s="2" t="n"/>
+      <c r="CP21" s="2" t="n"/>
+      <c r="CQ21" s="2" t="n"/>
+      <c r="CR21" s="2" t="n"/>
+      <c r="CS21" s="2" t="n"/>
+      <c r="CT21" s="2" t="n"/>
+      <c r="CU21" s="2" t="n"/>
+      <c r="CV21" s="2" t="n"/>
+      <c r="CW21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>200-TK-01</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>TANQUES</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Tanque de agua clarificada DAF</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Recepción de agua clarificada</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Agua residual no domestica</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>POLIETILENO</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="n"/>
+      <c r="U22" s="2" t="n"/>
+      <c r="V22" s="2" t="n"/>
+      <c r="W22" s="2" t="n"/>
+      <c r="X22" s="2" t="n"/>
+      <c r="Y22" s="2" t="n"/>
+      <c r="Z22" s="2" t="n"/>
+      <c r="AA22" s="2" t="n"/>
+      <c r="AB22" s="2" t="n"/>
+      <c r="AC22" s="2" t="n"/>
+      <c r="AD22" s="2" t="n"/>
+      <c r="AE22" s="2" t="n"/>
+      <c r="AF22" s="2" t="n"/>
+      <c r="AG22" s="2" t="n"/>
+      <c r="AH22" s="2" t="n"/>
+      <c r="AI22" s="2" t="n"/>
+      <c r="AJ22" s="2" t="n"/>
+      <c r="AK22" s="2" t="n"/>
+      <c r="AL22" s="2" t="n"/>
+      <c r="AM22" s="2" t="n"/>
+      <c r="AN22" s="2" t="n"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="AP22" s="2" t="inlineStr">
+        <is>
+          <t>12100</t>
+        </is>
+      </c>
+      <c r="AQ22" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AR22" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AS22" s="2" t="n"/>
+      <c r="AT22" s="2" t="n"/>
+      <c r="AU22" s="2" t="n"/>
+      <c r="AV22" s="2" t="n"/>
+      <c r="AW22" s="2" t="n"/>
+      <c r="AX22" s="2" t="n"/>
+      <c r="AY22" s="2" t="n"/>
+      <c r="AZ22" s="2" t="n"/>
+      <c r="BA22" s="2" t="n"/>
+      <c r="BB22" s="2" t="n"/>
+      <c r="BC22" s="2" t="n"/>
+      <c r="BD22" s="2" t="n"/>
+      <c r="BE22" s="2" t="n"/>
+      <c r="BF22" s="2" t="n"/>
+      <c r="BG22" s="2" t="n"/>
+      <c r="BH22" s="2" t="n"/>
+      <c r="BI22" s="2" t="n"/>
+      <c r="BJ22" s="2" t="n"/>
+      <c r="BK22" s="2" t="n"/>
+      <c r="BL22" s="2" t="n"/>
+      <c r="BM22" s="2" t="n"/>
+      <c r="BN22" s="2" t="n"/>
+      <c r="BO22" s="2" t="n"/>
+      <c r="BP22" s="2" t="n"/>
+      <c r="BQ22" s="2" t="n"/>
+      <c r="BR22" s="2" t="n"/>
+      <c r="BS22" s="2" t="n"/>
+      <c r="BT22" s="2" t="n"/>
+      <c r="BU22" s="2" t="n"/>
+      <c r="BV22" s="2" t="n"/>
+      <c r="BW22" s="2" t="n"/>
+      <c r="BX22" s="2" t="n"/>
+      <c r="BY22" s="2" t="n"/>
+      <c r="BZ22" s="2" t="n"/>
+      <c r="CA22" s="2" t="n"/>
+      <c r="CB22" s="2" t="n"/>
+      <c r="CC22" s="2" t="n"/>
+      <c r="CD22" s="2" t="n"/>
+      <c r="CE22" s="2" t="n"/>
+      <c r="CF22" s="2" t="n"/>
+      <c r="CG22" s="2" t="n"/>
+      <c r="CH22" s="2" t="n"/>
+      <c r="CI22" s="2" t="n"/>
+      <c r="CJ22" s="2" t="n"/>
+      <c r="CK22" s="2" t="n"/>
+      <c r="CL22" s="2" t="n"/>
+      <c r="CM22" s="2" t="n"/>
+      <c r="CN22" s="2" t="n"/>
+      <c r="CO22" s="2" t="n"/>
+      <c r="CP22" s="2" t="n"/>
+      <c r="CQ22" s="2" t="n"/>
+      <c r="CR22" s="2" t="n"/>
+      <c r="CS22" s="2" t="n"/>
+      <c r="CT22" s="2" t="n"/>
+      <c r="CU22" s="2" t="n"/>
+      <c r="CV22" s="2" t="n"/>
+      <c r="CW22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>600-TK-01</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>TANQUES</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Tanque de recepción de lodos</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Recpeción de Lodos Fisicoquímicos y Biológicos</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Lodo fisicoquímico y Biológico</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>POLIETILENO</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="n"/>
+      <c r="U23" s="2" t="n"/>
+      <c r="V23" s="2" t="n"/>
+      <c r="W23" s="2" t="n"/>
+      <c r="X23" s="2" t="n"/>
+      <c r="Y23" s="2" t="n"/>
+      <c r="Z23" s="2" t="n"/>
+      <c r="AA23" s="2" t="n"/>
+      <c r="AB23" s="2" t="n"/>
+      <c r="AC23" s="2" t="n"/>
+      <c r="AD23" s="2" t="n"/>
+      <c r="AE23" s="2" t="n"/>
+      <c r="AF23" s="2" t="n"/>
+      <c r="AG23" s="2" t="n"/>
+      <c r="AH23" s="2" t="n"/>
+      <c r="AI23" s="2" t="n"/>
+      <c r="AJ23" s="2" t="n"/>
+      <c r="AK23" s="2" t="n"/>
+      <c r="AL23" s="2" t="n"/>
+      <c r="AM23" s="2" t="n"/>
+      <c r="AN23" s="2" t="n"/>
+      <c r="AO23" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="AP23" s="2" t="n"/>
+      <c r="AQ23" s="2" t="n"/>
+      <c r="AR23" s="2" t="n"/>
+      <c r="AS23" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AT23" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AU23" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AV23" s="2" t="n"/>
+      <c r="AW23" s="2" t="n"/>
+      <c r="AX23" s="2" t="n"/>
+      <c r="AY23" s="2" t="n"/>
+      <c r="AZ23" s="2" t="n"/>
+      <c r="BA23" s="2" t="n"/>
+      <c r="BB23" s="2" t="n"/>
+      <c r="BC23" s="2" t="n"/>
+      <c r="BD23" s="2" t="n"/>
+      <c r="BE23" s="2" t="n"/>
+      <c r="BF23" s="2" t="n"/>
+      <c r="BG23" s="2" t="n"/>
+      <c r="BH23" s="2" t="n"/>
+      <c r="BI23" s="2" t="n"/>
+      <c r="BJ23" s="2" t="n"/>
+      <c r="BK23" s="2" t="n"/>
+      <c r="BL23" s="2" t="n"/>
+      <c r="BM23" s="2" t="n"/>
+      <c r="BN23" s="2" t="n"/>
+      <c r="BO23" s="2" t="n"/>
+      <c r="BP23" s="2" t="n"/>
+      <c r="BQ23" s="2" t="n"/>
+      <c r="BR23" s="2" t="n"/>
+      <c r="BS23" s="2" t="n"/>
+      <c r="BT23" s="2" t="n"/>
+      <c r="BU23" s="2" t="n"/>
+      <c r="BV23" s="2" t="n"/>
+      <c r="BW23" s="2" t="n"/>
+      <c r="BX23" s="2" t="n"/>
+      <c r="BY23" s="2" t="n"/>
+      <c r="BZ23" s="2" t="n"/>
+      <c r="CA23" s="2" t="n"/>
+      <c r="CB23" s="2" t="n"/>
+      <c r="CC23" s="2" t="n"/>
+      <c r="CD23" s="2" t="n"/>
+      <c r="CE23" s="2" t="n"/>
+      <c r="CF23" s="2" t="n"/>
+      <c r="CG23" s="2" t="n"/>
+      <c r="CH23" s="2" t="n"/>
+      <c r="CI23" s="2" t="n"/>
+      <c r="CJ23" s="2" t="n"/>
+      <c r="CK23" s="2" t="n"/>
+      <c r="CL23" s="2" t="n"/>
+      <c r="CM23" s="2" t="n"/>
+      <c r="CN23" s="2" t="n"/>
+      <c r="CO23" s="2" t="n"/>
+      <c r="CP23" s="2" t="n"/>
+      <c r="CQ23" s="2" t="n"/>
+      <c r="CR23" s="2" t="n"/>
+      <c r="CS23" s="2" t="n"/>
+      <c r="CT23" s="2" t="n"/>
+      <c r="CU23" s="2" t="n"/>
+      <c r="CV23" s="2" t="n"/>
+      <c r="CW23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>802-TK-01</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>TANQUES</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Tanque de almacenamiento de floculante</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Almacenamiento de floculante</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Discontinua</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Floculante</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7 - 8</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>POLIETILENO</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="n"/>
+      <c r="U24" s="2" t="n"/>
+      <c r="V24" s="2" t="n"/>
+      <c r="W24" s="2" t="n"/>
+      <c r="X24" s="2" t="n"/>
+      <c r="Y24" s="2" t="n"/>
+      <c r="Z24" s="2" t="n"/>
+      <c r="AA24" s="2" t="n"/>
+      <c r="AB24" s="2" t="n"/>
+      <c r="AC24" s="2" t="n"/>
+      <c r="AD24" s="2" t="n"/>
+      <c r="AE24" s="2" t="n"/>
+      <c r="AF24" s="2" t="n"/>
+      <c r="AG24" s="2" t="n"/>
+      <c r="AH24" s="2" t="n"/>
+      <c r="AI24" s="2" t="n"/>
+      <c r="AJ24" s="2" t="n"/>
+      <c r="AK24" s="2" t="n"/>
+      <c r="AL24" s="2" t="n"/>
+      <c r="AM24" s="2" t="n"/>
+      <c r="AN24" s="2" t="n"/>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="AP24" s="2" t="n"/>
+      <c r="AQ24" s="2" t="n"/>
+      <c r="AR24" s="2" t="n"/>
+      <c r="AS24" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AT24" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AU24" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AV24" s="2" t="n"/>
+      <c r="AW24" s="2" t="n"/>
+      <c r="AX24" s="2" t="n"/>
+      <c r="AY24" s="2" t="n"/>
+      <c r="AZ24" s="2" t="n"/>
+      <c r="BA24" s="2" t="n"/>
+      <c r="BB24" s="2" t="n"/>
+      <c r="BC24" s="2" t="n"/>
+      <c r="BD24" s="2" t="n"/>
+      <c r="BE24" s="2" t="n"/>
+      <c r="BF24" s="2" t="n"/>
+      <c r="BG24" s="2" t="n"/>
+      <c r="BH24" s="2" t="n"/>
+      <c r="BI24" s="2" t="n"/>
+      <c r="BJ24" s="2" t="n"/>
+      <c r="BK24" s="2" t="n"/>
+      <c r="BL24" s="2" t="n"/>
+      <c r="BM24" s="2" t="n"/>
+      <c r="BN24" s="2" t="n"/>
+      <c r="BO24" s="2" t="n"/>
+      <c r="BP24" s="2" t="n"/>
+      <c r="BQ24" s="2" t="n"/>
+      <c r="BR24" s="2" t="n"/>
+      <c r="BS24" s="2" t="n"/>
+      <c r="BT24" s="2" t="n"/>
+      <c r="BU24" s="2" t="n"/>
+      <c r="BV24" s="2" t="n"/>
+      <c r="BW24" s="2" t="n"/>
+      <c r="BX24" s="2" t="n"/>
+      <c r="BY24" s="2" t="n"/>
+      <c r="BZ24" s="2" t="n"/>
+      <c r="CA24" s="2" t="n"/>
+      <c r="CB24" s="2" t="n"/>
+      <c r="CC24" s="2" t="n"/>
+      <c r="CD24" s="2" t="n"/>
+      <c r="CE24" s="2" t="n"/>
+      <c r="CF24" s="2" t="n"/>
+      <c r="CG24" s="2" t="n"/>
+      <c r="CH24" s="2" t="n"/>
+      <c r="CI24" s="2" t="n"/>
+      <c r="CJ24" s="2" t="n"/>
+      <c r="CK24" s="2" t="n"/>
+      <c r="CL24" s="2" t="n"/>
+      <c r="CM24" s="2" t="n"/>
+      <c r="CN24" s="2" t="n"/>
+      <c r="CO24" s="2" t="n"/>
+      <c r="CP24" s="2" t="n"/>
+      <c r="CQ24" s="2" t="n"/>
+      <c r="CR24" s="2" t="n"/>
+      <c r="CS24" s="2" t="n"/>
+      <c r="CT24" s="2" t="n"/>
+      <c r="CU24" s="2" t="n"/>
+      <c r="CV24" s="2" t="n"/>
+      <c r="CW24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>803-TK-01</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>TANQUES</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Tanque de almacenamiento de deshidratante</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Almacenamiento de deshidratante</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Discontinua</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Deshidratante</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7 - 8</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>POLIETILENO</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="n"/>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="n"/>
+      <c r="W25" s="2" t="n"/>
+      <c r="X25" s="2" t="n"/>
+      <c r="Y25" s="2" t="n"/>
+      <c r="Z25" s="2" t="n"/>
+      <c r="AA25" s="2" t="n"/>
+      <c r="AB25" s="2" t="n"/>
+      <c r="AC25" s="2" t="n"/>
+      <c r="AD25" s="2" t="n"/>
+      <c r="AE25" s="2" t="n"/>
+      <c r="AF25" s="2" t="n"/>
+      <c r="AG25" s="2" t="n"/>
+      <c r="AH25" s="2" t="n"/>
+      <c r="AI25" s="2" t="n"/>
+      <c r="AJ25" s="2" t="n"/>
+      <c r="AK25" s="2" t="n"/>
+      <c r="AL25" s="2" t="n"/>
+      <c r="AM25" s="2" t="n"/>
+      <c r="AN25" s="2" t="n"/>
+      <c r="AO25" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="AP25" s="2" t="n"/>
+      <c r="AQ25" s="2" t="n"/>
+      <c r="AR25" s="2" t="n"/>
+      <c r="AS25" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AT25" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AU25" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AV25" s="2" t="n"/>
+      <c r="AW25" s="2" t="n"/>
+      <c r="AX25" s="2" t="n"/>
+      <c r="AY25" s="2" t="n"/>
+      <c r="AZ25" s="2" t="n"/>
+      <c r="BA25" s="2" t="n"/>
+      <c r="BB25" s="2" t="n"/>
+      <c r="BC25" s="2" t="n"/>
+      <c r="BD25" s="2" t="n"/>
+      <c r="BE25" s="2" t="n"/>
+      <c r="BF25" s="2" t="n"/>
+      <c r="BG25" s="2" t="n"/>
+      <c r="BH25" s="2" t="n"/>
+      <c r="BI25" s="2" t="n"/>
+      <c r="BJ25" s="2" t="n"/>
+      <c r="BK25" s="2" t="n"/>
+      <c r="BL25" s="2" t="n"/>
+      <c r="BM25" s="2" t="n"/>
+      <c r="BN25" s="2" t="n"/>
+      <c r="BO25" s="2" t="n"/>
+      <c r="BP25" s="2" t="n"/>
+      <c r="BQ25" s="2" t="n"/>
+      <c r="BR25" s="2" t="n"/>
+      <c r="BS25" s="2" t="n"/>
+      <c r="BT25" s="2" t="n"/>
+      <c r="BU25" s="2" t="n"/>
+      <c r="BV25" s="2" t="n"/>
+      <c r="BW25" s="2" t="n"/>
+      <c r="BX25" s="2" t="n"/>
+      <c r="BY25" s="2" t="n"/>
+      <c r="BZ25" s="2" t="n"/>
+      <c r="CA25" s="2" t="n"/>
+      <c r="CB25" s="2" t="n"/>
+      <c r="CC25" s="2" t="n"/>
+      <c r="CD25" s="2" t="n"/>
+      <c r="CE25" s="2" t="n"/>
+      <c r="CF25" s="2" t="n"/>
+      <c r="CG25" s="2" t="n"/>
+      <c r="CH25" s="2" t="n"/>
+      <c r="CI25" s="2" t="n"/>
+      <c r="CJ25" s="2" t="n"/>
+      <c r="CK25" s="2" t="n"/>
+      <c r="CL25" s="2" t="n"/>
+      <c r="CM25" s="2" t="n"/>
+      <c r="CN25" s="2" t="n"/>
+      <c r="CO25" s="2" t="n"/>
+      <c r="CP25" s="2" t="n"/>
+      <c r="CQ25" s="2" t="n"/>
+      <c r="CR25" s="2" t="n"/>
+      <c r="CS25" s="2" t="n"/>
+      <c r="CT25" s="2" t="n"/>
+      <c r="CU25" s="2" t="n"/>
+      <c r="CV25" s="2" t="n"/>
+      <c r="CW25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>807-TK-01</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>TANQUES</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Tanque de almacenamiento de nutrientes</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Almacenamiento de nutrientes</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Discontinua</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Nutrientes</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>7 - 8</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>POLIETILENO</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="n"/>
+      <c r="W26" s="2" t="n"/>
+      <c r="X26" s="2" t="n"/>
+      <c r="Y26" s="2" t="n"/>
+      <c r="Z26" s="2" t="n"/>
+      <c r="AA26" s="2" t="n"/>
+      <c r="AB26" s="2" t="n"/>
+      <c r="AC26" s="2" t="n"/>
+      <c r="AD26" s="2" t="n"/>
+      <c r="AE26" s="2" t="n"/>
+      <c r="AF26" s="2" t="n"/>
+      <c r="AG26" s="2" t="n"/>
+      <c r="AH26" s="2" t="n"/>
+      <c r="AI26" s="2" t="n"/>
+      <c r="AJ26" s="2" t="n"/>
+      <c r="AK26" s="2" t="n"/>
+      <c r="AL26" s="2" t="n"/>
+      <c r="AM26" s="2" t="n"/>
+      <c r="AN26" s="2" t="n"/>
+      <c r="AO26" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="AP26" s="2" t="n"/>
+      <c r="AQ26" s="2" t="n"/>
+      <c r="AR26" s="2" t="n"/>
+      <c r="AS26" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AT26" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AU26" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AV26" s="2" t="n"/>
+      <c r="AW26" s="2" t="n"/>
+      <c r="AX26" s="2" t="n"/>
+      <c r="AY26" s="2" t="n"/>
+      <c r="AZ26" s="2" t="n"/>
+      <c r="BA26" s="2" t="n"/>
+      <c r="BB26" s="2" t="n"/>
+      <c r="BC26" s="2" t="n"/>
+      <c r="BD26" s="2" t="n"/>
+      <c r="BE26" s="2" t="n"/>
+      <c r="BF26" s="2" t="n"/>
+      <c r="BG26" s="2" t="n"/>
+      <c r="BH26" s="2" t="n"/>
+      <c r="BI26" s="2" t="n"/>
+      <c r="BJ26" s="2" t="n"/>
+      <c r="BK26" s="2" t="n"/>
+      <c r="BL26" s="2" t="n"/>
+      <c r="BM26" s="2" t="n"/>
+      <c r="BN26" s="2" t="n"/>
+      <c r="BO26" s="2" t="n"/>
+      <c r="BP26" s="2" t="n"/>
+      <c r="BQ26" s="2" t="n"/>
+      <c r="BR26" s="2" t="n"/>
+      <c r="BS26" s="2" t="n"/>
+      <c r="BT26" s="2" t="n"/>
+      <c r="BU26" s="2" t="n"/>
+      <c r="BV26" s="2" t="n"/>
+      <c r="BW26" s="2" t="n"/>
+      <c r="BX26" s="2" t="n"/>
+      <c r="BY26" s="2" t="n"/>
+      <c r="BZ26" s="2" t="n"/>
+      <c r="CA26" s="2" t="n"/>
+      <c r="CB26" s="2" t="n"/>
+      <c r="CC26" s="2" t="n"/>
+      <c r="CD26" s="2" t="n"/>
+      <c r="CE26" s="2" t="n"/>
+      <c r="CF26" s="2" t="n"/>
+      <c r="CG26" s="2" t="n"/>
+      <c r="CH26" s="2" t="n"/>
+      <c r="CI26" s="2" t="n"/>
+      <c r="CJ26" s="2" t="n"/>
+      <c r="CK26" s="2" t="n"/>
+      <c r="CL26" s="2" t="n"/>
+      <c r="CM26" s="2" t="n"/>
+      <c r="CN26" s="2" t="n"/>
+      <c r="CO26" s="2" t="n"/>
+      <c r="CP26" s="2" t="n"/>
+      <c r="CQ26" s="2" t="n"/>
+      <c r="CR26" s="2" t="n"/>
+      <c r="CS26" s="2" t="n"/>
+      <c r="CT26" s="2" t="n"/>
+      <c r="CU26" s="2" t="n"/>
+      <c r="CV26" s="2" t="n"/>
+      <c r="CW26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>200-PS-01</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>EQUIPOS</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Celda de flotación aire disuelto - DAF</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Separación sólido - Líquido</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Agua residual no domestica</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>PRFV</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="n"/>
+      <c r="U27" s="2" t="n"/>
+      <c r="V27" s="2" t="n"/>
+      <c r="W27" s="2" t="n"/>
+      <c r="X27" s="2" t="n"/>
+      <c r="Y27" s="2" t="n"/>
+      <c r="Z27" s="2" t="n"/>
+      <c r="AA27" s="2" t="n"/>
+      <c r="AB27" s="2" t="n"/>
+      <c r="AC27" s="2" t="n"/>
+      <c r="AD27" s="2" t="n"/>
+      <c r="AE27" s="2" t="n"/>
+      <c r="AF27" s="2" t="n"/>
+      <c r="AG27" s="2" t="n"/>
+      <c r="AH27" s="2" t="n"/>
+      <c r="AI27" s="2" t="n"/>
+      <c r="AJ27" s="2" t="n"/>
+      <c r="AK27" s="2" t="n"/>
+      <c r="AL27" s="2" t="n"/>
+      <c r="AM27" s="2" t="n"/>
+      <c r="AN27" s="2" t="n"/>
+      <c r="AO27" s="2" t="n"/>
+      <c r="AP27" s="2" t="n"/>
+      <c r="AQ27" s="2" t="n"/>
+      <c r="AR27" s="2" t="n"/>
+      <c r="AS27" s="2" t="n"/>
+      <c r="AT27" s="2" t="n"/>
+      <c r="AU27" s="2" t="n"/>
+      <c r="AV27" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="AW27" s="2" t="inlineStr">
+        <is>
+          <t>2256</t>
+        </is>
+      </c>
+      <c r="AX27" s="2" t="n"/>
+      <c r="AY27" s="2" t="n"/>
+      <c r="AZ27" s="2" t="n"/>
+      <c r="BA27" s="2" t="n"/>
+      <c r="BB27" s="2" t="n"/>
+      <c r="BC27" s="2" t="n"/>
+      <c r="BD27" s="2" t="n"/>
+      <c r="BE27" s="2" t="n"/>
+      <c r="BF27" s="2" t="n"/>
+      <c r="BG27" s="2" t="n"/>
+      <c r="BH27" s="2" t="n"/>
+      <c r="BI27" s="2" t="n"/>
+      <c r="BJ27" s="2" t="n"/>
+      <c r="BK27" s="2" t="n"/>
+      <c r="BL27" s="2" t="n"/>
+      <c r="BM27" s="2" t="n"/>
+      <c r="BN27" s="2" t="n"/>
+      <c r="BO27" s="2" t="n"/>
+      <c r="BP27" s="2" t="n"/>
+      <c r="BQ27" s="2" t="n"/>
+      <c r="BR27" s="2" t="n"/>
+      <c r="BS27" s="2" t="n"/>
+      <c r="BT27" s="2" t="n"/>
+      <c r="BU27" s="2" t="n"/>
+      <c r="BV27" s="2" t="n"/>
+      <c r="BW27" s="2" t="n"/>
+      <c r="BX27" s="2" t="n"/>
+      <c r="BY27" s="2" t="n"/>
+      <c r="BZ27" s="2" t="n"/>
+      <c r="CA27" s="2" t="n"/>
+      <c r="CB27" s="2" t="n"/>
+      <c r="CC27" s="2" t="n"/>
+      <c r="CD27" s="2" t="n"/>
+      <c r="CE27" s="2" t="n"/>
+      <c r="CF27" s="2" t="n"/>
+      <c r="CG27" s="2" t="n"/>
+      <c r="CH27" s="2" t="n"/>
+      <c r="CI27" s="2" t="n"/>
+      <c r="CJ27" s="2" t="n"/>
+      <c r="CK27" s="2" t="n"/>
+      <c r="CL27" s="2" t="n"/>
+      <c r="CM27" s="2" t="n"/>
+      <c r="CN27" s="2" t="n"/>
+      <c r="CO27" s="2" t="n"/>
+      <c r="CP27" s="2" t="n"/>
+      <c r="CQ27" s="2" t="n"/>
+      <c r="CR27" s="2" t="n"/>
+      <c r="CS27" s="2" t="n"/>
+      <c r="CT27" s="2" t="n"/>
+      <c r="CU27" s="2" t="n"/>
+      <c r="CV27" s="2" t="n"/>
+      <c r="CW27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>400-C-01A</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>EQUIPOS</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Soplador</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Suministro de Aire atmosférico al MBBR 1/MBBR 2/ MBBR 3/ MBBR 4; Tanques de homogenización 100-TK-01/02; Tanque de recepción de lodos 600-TK-01 y acondicionamiento de lodo 600-TK-02; Tanque de floculante 802-TK-01; Tanque de deshidratante 803-TK-01; Tanque de nutrientes 807-TK-01</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Discontinua</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Aire</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="n"/>
+      <c r="U28" s="2" t="n"/>
+      <c r="V28" s="2" t="n"/>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="CZ21" s="2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="DA21" s="2" t="inlineStr">
-        <is>
-          <t>220/440 DOBLE ESTRELLA / ESTRELLA</t>
-        </is>
-      </c>
-      <c r="DB21" s="2" t="inlineStr">
-        <is>
-          <t>6.30 / 3.15</t>
-        </is>
-      </c>
-      <c r="DC21" s="2" t="inlineStr">
+      <c r="Y28" s="2" t="n"/>
+      <c r="Z28" s="2" t="n"/>
+      <c r="AA28" s="2" t="n"/>
+      <c r="AB28" s="2" t="n"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>PW 5246</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="n"/>
+      <c r="AE28" s="2" t="n"/>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>Regenerativo</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="n"/>
+      <c r="AH28" s="2" t="n"/>
+      <c r="AI28" s="2" t="n"/>
+      <c r="AJ28" s="2" t="n"/>
+      <c r="AK28" s="2" t="n"/>
+      <c r="AL28" s="2" t="n"/>
+      <c r="AM28" s="2" t="n"/>
+      <c r="AN28" s="2" t="n"/>
+      <c r="AO28" s="2" t="n"/>
+      <c r="AP28" s="2" t="n"/>
+      <c r="AQ28" s="2" t="n"/>
+      <c r="AR28" s="2" t="n"/>
+      <c r="AS28" s="2" t="n"/>
+      <c r="AT28" s="2" t="n"/>
+      <c r="AU28" s="2" t="n"/>
+      <c r="AV28" s="2" t="n"/>
+      <c r="AW28" s="2" t="n"/>
+      <c r="AX28" s="2" t="inlineStr">
+        <is>
+          <t>20 - 25</t>
+        </is>
+      </c>
+      <c r="AY28" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AZ28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BA28" s="2" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="BB28" s="2" t="inlineStr">
+        <is>
+          <t>3460</t>
+        </is>
+      </c>
+      <c r="BC28" s="2" t="inlineStr">
+        <is>
+          <t>220V 12,6 A</t>
+        </is>
+      </c>
+      <c r="BD28" s="2" t="inlineStr">
+        <is>
+          <t>-380</t>
+        </is>
+      </c>
+      <c r="BE28" s="2" t="n"/>
+      <c r="BF28" s="2" t="n"/>
+      <c r="BG28" s="2" t="n"/>
+      <c r="BH28" s="2" t="n"/>
+      <c r="BI28" s="2" t="n"/>
+      <c r="BJ28" s="2" t="n"/>
+      <c r="BK28" s="2" t="n"/>
+      <c r="BL28" s="2" t="n"/>
+      <c r="BM28" s="2" t="n"/>
+      <c r="BN28" s="2" t="n"/>
+      <c r="BO28" s="2" t="n"/>
+      <c r="BP28" s="2" t="n"/>
+      <c r="BQ28" s="2" t="n"/>
+      <c r="BR28" s="2" t="n"/>
+      <c r="BS28" s="2" t="n"/>
+      <c r="BT28" s="2" t="n"/>
+      <c r="BU28" s="2" t="n"/>
+      <c r="BV28" s="2" t="n"/>
+      <c r="BW28" s="2" t="n"/>
+      <c r="BX28" s="2" t="n"/>
+      <c r="BY28" s="2" t="n"/>
+      <c r="BZ28" s="2" t="n"/>
+      <c r="CA28" s="2" t="n"/>
+      <c r="CB28" s="2" t="n"/>
+      <c r="CC28" s="2" t="n"/>
+      <c r="CD28" s="2" t="n"/>
+      <c r="CE28" s="2" t="n"/>
+      <c r="CF28" s="2" t="n"/>
+      <c r="CG28" s="2" t="n"/>
+      <c r="CH28" s="2" t="n"/>
+      <c r="CI28" s="2" t="n"/>
+      <c r="CJ28" s="2" t="n"/>
+      <c r="CK28" s="2" t="n"/>
+      <c r="CL28" s="2" t="n"/>
+      <c r="CM28" s="2" t="n"/>
+      <c r="CN28" s="2" t="n"/>
+      <c r="CO28" s="2" t="n"/>
+      <c r="CP28" s="2" t="n"/>
+      <c r="CQ28" s="2" t="n"/>
+      <c r="CR28" s="2" t="n"/>
+      <c r="CS28" s="2" t="n"/>
+      <c r="CT28" s="2" t="n"/>
+      <c r="CU28" s="2" t="n"/>
+      <c r="CV28" s="2" t="n"/>
+      <c r="CW28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>400-C-01B</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>EQUIPOS</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Soplador</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Suministro de Aire atmosférico al MBBR 1/MBBR 2/ MBBR 3/ MBBR 4; Tanques de homogenización 100-TK-01/02; Tanque de recepción de lodos 600-TK-01 y acondicionamiento de lodo 600-TK-02; Tanque de floculante 802-TK-01; Tanque de deshidratante 803-TK-01; Tanque de nutrientes 807-TK-01</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Discontinua</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Aire</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
+      <c r="T29" s="2" t="n"/>
+      <c r="U29" s="2" t="n"/>
+      <c r="V29" s="2" t="n"/>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="n"/>
+      <c r="Z29" s="2" t="n"/>
+      <c r="AA29" s="2" t="n"/>
+      <c r="AB29" s="2" t="n"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>PW 5246</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="n"/>
+      <c r="AE29" s="2" t="n"/>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>Regenerativo</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="n"/>
+      <c r="AH29" s="2" t="n"/>
+      <c r="AI29" s="2" t="n"/>
+      <c r="AJ29" s="2" t="n"/>
+      <c r="AK29" s="2" t="n"/>
+      <c r="AL29" s="2" t="n"/>
+      <c r="AM29" s="2" t="n"/>
+      <c r="AN29" s="2" t="n"/>
+      <c r="AO29" s="2" t="n"/>
+      <c r="AP29" s="2" t="n"/>
+      <c r="AQ29" s="2" t="n"/>
+      <c r="AR29" s="2" t="n"/>
+      <c r="AS29" s="2" t="n"/>
+      <c r="AT29" s="2" t="n"/>
+      <c r="AU29" s="2" t="n"/>
+      <c r="AV29" s="2" t="n"/>
+      <c r="AW29" s="2" t="n"/>
+      <c r="AX29" s="2" t="inlineStr">
+        <is>
+          <t>20 - 25</t>
+        </is>
+      </c>
+      <c r="AY29" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AZ29" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BA29" s="2" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="BB29" s="2" t="inlineStr">
+        <is>
+          <t>3460</t>
+        </is>
+      </c>
+      <c r="BC29" s="2" t="inlineStr">
+        <is>
+          <t>220V 12,6 A</t>
+        </is>
+      </c>
+      <c r="BD29" s="2" t="inlineStr">
+        <is>
+          <t>-380</t>
+        </is>
+      </c>
+      <c r="BE29" s="2" t="n"/>
+      <c r="BF29" s="2" t="n"/>
+      <c r="BG29" s="2" t="n"/>
+      <c r="BH29" s="2" t="n"/>
+      <c r="BI29" s="2" t="n"/>
+      <c r="BJ29" s="2" t="n"/>
+      <c r="BK29" s="2" t="n"/>
+      <c r="BL29" s="2" t="n"/>
+      <c r="BM29" s="2" t="n"/>
+      <c r="BN29" s="2" t="n"/>
+      <c r="BO29" s="2" t="n"/>
+      <c r="BP29" s="2" t="n"/>
+      <c r="BQ29" s="2" t="n"/>
+      <c r="BR29" s="2" t="n"/>
+      <c r="BS29" s="2" t="n"/>
+      <c r="BT29" s="2" t="n"/>
+      <c r="BU29" s="2" t="n"/>
+      <c r="BV29" s="2" t="n"/>
+      <c r="BW29" s="2" t="n"/>
+      <c r="BX29" s="2" t="n"/>
+      <c r="BY29" s="2" t="n"/>
+      <c r="BZ29" s="2" t="n"/>
+      <c r="CA29" s="2" t="n"/>
+      <c r="CB29" s="2" t="n"/>
+      <c r="CC29" s="2" t="n"/>
+      <c r="CD29" s="2" t="n"/>
+      <c r="CE29" s="2" t="n"/>
+      <c r="CF29" s="2" t="n"/>
+      <c r="CG29" s="2" t="n"/>
+      <c r="CH29" s="2" t="n"/>
+      <c r="CI29" s="2" t="n"/>
+      <c r="CJ29" s="2" t="n"/>
+      <c r="CK29" s="2" t="n"/>
+      <c r="CL29" s="2" t="n"/>
+      <c r="CM29" s="2" t="n"/>
+      <c r="CN29" s="2" t="n"/>
+      <c r="CO29" s="2" t="n"/>
+      <c r="CP29" s="2" t="n"/>
+      <c r="CQ29" s="2" t="n"/>
+      <c r="CR29" s="2" t="n"/>
+      <c r="CS29" s="2" t="n"/>
+      <c r="CT29" s="2" t="n"/>
+      <c r="CU29" s="2" t="n"/>
+      <c r="CV29" s="2" t="n"/>
+      <c r="CW29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>500-TK-01</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>TANQUES</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Tanque de agua filtrada</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Recepción de agua filtrada para retrolavado/Vertimiento final</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Agua residual no domestica</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>POLIETILENO</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="2" t="n"/>
+      <c r="U30" s="2" t="n"/>
+      <c r="V30" s="2" t="n"/>
+      <c r="W30" s="2" t="n"/>
+      <c r="X30" s="2" t="n"/>
+      <c r="Y30" s="2" t="n"/>
+      <c r="Z30" s="2" t="n"/>
+      <c r="AA30" s="2" t="n"/>
+      <c r="AB30" s="2" t="n"/>
+      <c r="AC30" s="2" t="n"/>
+      <c r="AD30" s="2" t="n"/>
+      <c r="AE30" s="2" t="n"/>
+      <c r="AF30" s="2" t="n"/>
+      <c r="AG30" s="2" t="n"/>
+      <c r="AH30" s="2" t="n"/>
+      <c r="AI30" s="2" t="n"/>
+      <c r="AJ30" s="2" t="n"/>
+      <c r="AK30" s="2" t="n"/>
+      <c r="AL30" s="2" t="n"/>
+      <c r="AM30" s="2" t="n"/>
+      <c r="AN30" s="2" t="n"/>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="AP30" s="2" t="n"/>
+      <c r="AQ30" s="2" t="n"/>
+      <c r="AR30" s="2" t="n"/>
+      <c r="AS30" s="2" t="n"/>
+      <c r="AT30" s="2" t="n"/>
+      <c r="AU30" s="2" t="n"/>
+      <c r="AV30" s="2" t="n"/>
+      <c r="AW30" s="2" t="n"/>
+      <c r="AX30" s="2" t="n"/>
+      <c r="AY30" s="2" t="n"/>
+      <c r="AZ30" s="2" t="n"/>
+      <c r="BA30" s="2" t="n"/>
+      <c r="BB30" s="2" t="n"/>
+      <c r="BC30" s="2" t="n"/>
+      <c r="BD30" s="2" t="n"/>
+      <c r="BE30" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="BF30" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="BG30" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="BH30" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="BI30" s="2" t="n"/>
+      <c r="BJ30" s="2" t="n"/>
+      <c r="BK30" s="2" t="n"/>
+      <c r="BL30" s="2" t="n"/>
+      <c r="BM30" s="2" t="n"/>
+      <c r="BN30" s="2" t="n"/>
+      <c r="BO30" s="2" t="n"/>
+      <c r="BP30" s="2" t="n"/>
+      <c r="BQ30" s="2" t="n"/>
+      <c r="BR30" s="2" t="n"/>
+      <c r="BS30" s="2" t="n"/>
+      <c r="BT30" s="2" t="n"/>
+      <c r="BU30" s="2" t="n"/>
+      <c r="BV30" s="2" t="n"/>
+      <c r="BW30" s="2" t="n"/>
+      <c r="BX30" s="2" t="n"/>
+      <c r="BY30" s="2" t="n"/>
+      <c r="BZ30" s="2" t="n"/>
+      <c r="CA30" s="2" t="n"/>
+      <c r="CB30" s="2" t="n"/>
+      <c r="CC30" s="2" t="n"/>
+      <c r="CD30" s="2" t="n"/>
+      <c r="CE30" s="2" t="n"/>
+      <c r="CF30" s="2" t="n"/>
+      <c r="CG30" s="2" t="n"/>
+      <c r="CH30" s="2" t="n"/>
+      <c r="CI30" s="2" t="n"/>
+      <c r="CJ30" s="2" t="n"/>
+      <c r="CK30" s="2" t="n"/>
+      <c r="CL30" s="2" t="n"/>
+      <c r="CM30" s="2" t="n"/>
+      <c r="CN30" s="2" t="n"/>
+      <c r="CO30" s="2" t="n"/>
+      <c r="CP30" s="2" t="n"/>
+      <c r="CQ30" s="2" t="n"/>
+      <c r="CR30" s="2" t="n"/>
+      <c r="CS30" s="2" t="n"/>
+      <c r="CT30" s="2" t="n"/>
+      <c r="CU30" s="2" t="n"/>
+      <c r="CV30" s="2" t="n"/>
+      <c r="CW30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>600-TK-02</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>TANQUES</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Tanque de acondicionamiento de lodo</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Acondicionamiento de Lodos Fisicoquímicos y Biológicos</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Lodos</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>POLIETILENO</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="n"/>
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="n"/>
+      <c r="U31" s="2" t="n"/>
+      <c r="V31" s="2" t="n"/>
+      <c r="W31" s="2" t="n"/>
+      <c r="X31" s="2" t="n"/>
+      <c r="Y31" s="2" t="n"/>
+      <c r="Z31" s="2" t="n"/>
+      <c r="AA31" s="2" t="n"/>
+      <c r="AB31" s="2" t="n"/>
+      <c r="AC31" s="2" t="n"/>
+      <c r="AD31" s="2" t="n"/>
+      <c r="AE31" s="2" t="n"/>
+      <c r="AF31" s="2" t="n"/>
+      <c r="AG31" s="2" t="n"/>
+      <c r="AH31" s="2" t="n"/>
+      <c r="AI31" s="2" t="n"/>
+      <c r="AJ31" s="2" t="n"/>
+      <c r="AK31" s="2" t="n"/>
+      <c r="AL31" s="2" t="n"/>
+      <c r="AM31" s="2" t="n"/>
+      <c r="AN31" s="2" t="n"/>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="AP31" s="2" t="n"/>
+      <c r="AQ31" s="2" t="n"/>
+      <c r="AR31" s="2" t="n"/>
+      <c r="AS31" s="2" t="n"/>
+      <c r="AT31" s="2" t="n"/>
+      <c r="AU31" s="2" t="n"/>
+      <c r="AV31" s="2" t="n"/>
+      <c r="AW31" s="2" t="n"/>
+      <c r="AX31" s="2" t="n"/>
+      <c r="AY31" s="2" t="n"/>
+      <c r="AZ31" s="2" t="n"/>
+      <c r="BA31" s="2" t="n"/>
+      <c r="BB31" s="2" t="n"/>
+      <c r="BC31" s="2" t="n"/>
+      <c r="BD31" s="2" t="n"/>
+      <c r="BE31" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="BF31" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="BG31" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="BH31" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="BI31" s="2" t="n"/>
+      <c r="BJ31" s="2" t="n"/>
+      <c r="BK31" s="2" t="n"/>
+      <c r="BL31" s="2" t="n"/>
+      <c r="BM31" s="2" t="n"/>
+      <c r="BN31" s="2" t="n"/>
+      <c r="BO31" s="2" t="n"/>
+      <c r="BP31" s="2" t="n"/>
+      <c r="BQ31" s="2" t="n"/>
+      <c r="BR31" s="2" t="n"/>
+      <c r="BS31" s="2" t="n"/>
+      <c r="BT31" s="2" t="n"/>
+      <c r="BU31" s="2" t="n"/>
+      <c r="BV31" s="2" t="n"/>
+      <c r="BW31" s="2" t="n"/>
+      <c r="BX31" s="2" t="n"/>
+      <c r="BY31" s="2" t="n"/>
+      <c r="BZ31" s="2" t="n"/>
+      <c r="CA31" s="2" t="n"/>
+      <c r="CB31" s="2" t="n"/>
+      <c r="CC31" s="2" t="n"/>
+      <c r="CD31" s="2" t="n"/>
+      <c r="CE31" s="2" t="n"/>
+      <c r="CF31" s="2" t="n"/>
+      <c r="CG31" s="2" t="n"/>
+      <c r="CH31" s="2" t="n"/>
+      <c r="CI31" s="2" t="n"/>
+      <c r="CJ31" s="2" t="n"/>
+      <c r="CK31" s="2" t="n"/>
+      <c r="CL31" s="2" t="n"/>
+      <c r="CM31" s="2" t="n"/>
+      <c r="CN31" s="2" t="n"/>
+      <c r="CO31" s="2" t="n"/>
+      <c r="CP31" s="2" t="n"/>
+      <c r="CQ31" s="2" t="n"/>
+      <c r="CR31" s="2" t="n"/>
+      <c r="CS31" s="2" t="n"/>
+      <c r="CT31" s="2" t="n"/>
+      <c r="CU31" s="2" t="n"/>
+      <c r="CV31" s="2" t="n"/>
+      <c r="CW31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>500-F-01</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>TANQUES</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Filtro multimedia</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Retención de sólidos suspendidos</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Agua residual no domestica</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>Polyglass</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="n"/>
+      <c r="U32" s="2" t="n"/>
+      <c r="V32" s="2" t="n"/>
+      <c r="W32" s="2" t="n"/>
+      <c r="X32" s="2" t="n"/>
+      <c r="Y32" s="2" t="n"/>
+      <c r="Z32" s="2" t="n"/>
+      <c r="AA32" s="2" t="n"/>
+      <c r="AB32" s="2" t="n"/>
+      <c r="AC32" s="2" t="n"/>
+      <c r="AD32" s="2" t="n"/>
+      <c r="AE32" s="2" t="n"/>
+      <c r="AF32" s="2" t="inlineStr">
+        <is>
+          <t>Vaso presión</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="n"/>
+      <c r="AH32" s="2" t="n"/>
+      <c r="AI32" s="2" t="n"/>
+      <c r="AJ32" s="2" t="n"/>
+      <c r="AK32" s="2" t="n"/>
+      <c r="AL32" s="2" t="n"/>
+      <c r="AM32" s="2" t="n"/>
+      <c r="AN32" s="2" t="n"/>
+      <c r="AO32" s="2" t="n"/>
+      <c r="AP32" s="2" t="n"/>
+      <c r="AQ32" s="2" t="n"/>
+      <c r="AR32" s="2" t="n"/>
+      <c r="AS32" s="2" t="n"/>
+      <c r="AT32" s="2" t="n"/>
+      <c r="AU32" s="2" t="n"/>
+      <c r="AV32" s="2" t="n"/>
+      <c r="AW32" s="2" t="n"/>
+      <c r="AX32" s="2" t="n"/>
+      <c r="AY32" s="2" t="n"/>
+      <c r="AZ32" s="2" t="n"/>
+      <c r="BA32" s="2" t="n"/>
+      <c r="BB32" s="2" t="n"/>
+      <c r="BC32" s="2" t="n"/>
+      <c r="BD32" s="2" t="n"/>
+      <c r="BE32" s="2" t="n"/>
+      <c r="BF32" s="2" t="n"/>
+      <c r="BG32" s="2" t="n"/>
+      <c r="BH32" s="2" t="n"/>
+      <c r="BI32" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BJ32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK32" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BL32" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="BM32" s="2" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="DD21" s="2" t="inlineStr">
-        <is>
-          <t>R76 / 680430506</t>
-        </is>
-      </c>
-      <c r="DE21" s="2" t="inlineStr">
-        <is>
-          <t>155(F) / 55</t>
-        </is>
-      </c>
-      <c r="DF21" s="2" t="inlineStr">
-        <is>
-          <t>83.8 / 86.1 / 86.5</t>
-        </is>
-      </c>
-      <c r="DG21" s="2" t="n"/>
-      <c r="DH21" s="2" t="n"/>
+      <c r="BN32" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BO32" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BP32" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BQ32" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="BR32" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="BS32" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="BT32" s="2" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="BU32" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="BV32" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="BW32" s="2" t="n"/>
+      <c r="BX32" s="2" t="n"/>
+      <c r="BY32" s="2" t="n"/>
+      <c r="BZ32" s="2" t="n"/>
+      <c r="CA32" s="2" t="n"/>
+      <c r="CB32" s="2" t="n"/>
+      <c r="CC32" s="2" t="n"/>
+      <c r="CD32" s="2" t="n"/>
+      <c r="CE32" s="2" t="n"/>
+      <c r="CF32" s="2" t="n"/>
+      <c r="CG32" s="2" t="n"/>
+      <c r="CH32" s="2" t="n"/>
+      <c r="CI32" s="2" t="n"/>
+      <c r="CJ32" s="2" t="n"/>
+      <c r="CK32" s="2" t="n"/>
+      <c r="CL32" s="2" t="n"/>
+      <c r="CM32" s="2" t="n"/>
+      <c r="CN32" s="2" t="n"/>
+      <c r="CO32" s="2" t="n"/>
+      <c r="CP32" s="2" t="n"/>
+      <c r="CQ32" s="2" t="n"/>
+      <c r="CR32" s="2" t="n"/>
+      <c r="CS32" s="2" t="n"/>
+      <c r="CT32" s="2" t="n"/>
+      <c r="CU32" s="2" t="n"/>
+      <c r="CV32" s="2" t="n"/>
+      <c r="CW32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>500-F-02</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>TANQUES</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Filtro CAG</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Retención de materia orgánica</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Agua residual no domestica</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Polyglass</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="n"/>
+      <c r="U33" s="2" t="n"/>
+      <c r="V33" s="2" t="n"/>
+      <c r="W33" s="2" t="n"/>
+      <c r="X33" s="2" t="n"/>
+      <c r="Y33" s="2" t="n"/>
+      <c r="Z33" s="2" t="n"/>
+      <c r="AA33" s="2" t="n"/>
+      <c r="AB33" s="2" t="n"/>
+      <c r="AC33" s="2" t="n"/>
+      <c r="AD33" s="2" t="n"/>
+      <c r="AE33" s="2" t="n"/>
+      <c r="AF33" s="2" t="inlineStr">
+        <is>
+          <t>Vaso presión</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="n"/>
+      <c r="AH33" s="2" t="n"/>
+      <c r="AI33" s="2" t="n"/>
+      <c r="AJ33" s="2" t="n"/>
+      <c r="AK33" s="2" t="n"/>
+      <c r="AL33" s="2" t="n"/>
+      <c r="AM33" s="2" t="n"/>
+      <c r="AN33" s="2" t="n"/>
+      <c r="AO33" s="2" t="n"/>
+      <c r="AP33" s="2" t="n"/>
+      <c r="AQ33" s="2" t="n"/>
+      <c r="AR33" s="2" t="n"/>
+      <c r="AS33" s="2" t="n"/>
+      <c r="AT33" s="2" t="n"/>
+      <c r="AU33" s="2" t="n"/>
+      <c r="AV33" s="2" t="n"/>
+      <c r="AW33" s="2" t="n"/>
+      <c r="AX33" s="2" t="n"/>
+      <c r="AY33" s="2" t="n"/>
+      <c r="AZ33" s="2" t="n"/>
+      <c r="BA33" s="2" t="n"/>
+      <c r="BB33" s="2" t="n"/>
+      <c r="BC33" s="2" t="n"/>
+      <c r="BD33" s="2" t="n"/>
+      <c r="BE33" s="2" t="n"/>
+      <c r="BF33" s="2" t="n"/>
+      <c r="BG33" s="2" t="n"/>
+      <c r="BH33" s="2" t="n"/>
+      <c r="BI33" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BJ33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK33" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BL33" s="2" t="n"/>
+      <c r="BM33" s="2" t="n"/>
+      <c r="BN33" s="2" t="n"/>
+      <c r="BO33" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BP33" s="2" t="n"/>
+      <c r="BQ33" s="2" t="n"/>
+      <c r="BR33" s="2" t="n"/>
+      <c r="BS33" s="2" t="n"/>
+      <c r="BT33" s="2" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="BU33" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="BV33" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="BW33" s="2" t="inlineStr">
+        <is>
+          <t>5.13</t>
+        </is>
+      </c>
+      <c r="BX33" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BY33" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BZ33" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="CA33" s="2" t="n"/>
+      <c r="CB33" s="2" t="n"/>
+      <c r="CC33" s="2" t="n"/>
+      <c r="CD33" s="2" t="n"/>
+      <c r="CE33" s="2" t="n"/>
+      <c r="CF33" s="2" t="n"/>
+      <c r="CG33" s="2" t="n"/>
+      <c r="CH33" s="2" t="n"/>
+      <c r="CI33" s="2" t="n"/>
+      <c r="CJ33" s="2" t="n"/>
+      <c r="CK33" s="2" t="n"/>
+      <c r="CL33" s="2" t="n"/>
+      <c r="CM33" s="2" t="n"/>
+      <c r="CN33" s="2" t="n"/>
+      <c r="CO33" s="2" t="n"/>
+      <c r="CP33" s="2" t="n"/>
+      <c r="CQ33" s="2" t="n"/>
+      <c r="CR33" s="2" t="n"/>
+      <c r="CS33" s="2" t="n"/>
+      <c r="CT33" s="2" t="n"/>
+      <c r="CU33" s="2" t="n"/>
+      <c r="CV33" s="2" t="n"/>
+      <c r="CW33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>600-P-02</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>EQUIPOS</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Bomba trasiego de lixiviados</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Trasiego ARnD desde foso de lixiviados 600-TK-03 hacia tanques 100-TK-01/02</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Discontinua</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Lixiviados</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>Cuerpo: Polipropileno
+Diafragma PTFE</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="n"/>
+      <c r="U34" s="2" t="n"/>
+      <c r="V34" s="2" t="n"/>
+      <c r="W34" s="2" t="n"/>
+      <c r="X34" s="2" t="n"/>
+      <c r="Y34" s="2" t="n"/>
+      <c r="Z34" s="2" t="n"/>
+      <c r="AA34" s="2" t="n"/>
+      <c r="AB34" s="2" t="n"/>
+      <c r="AC34" s="2" t="n"/>
+      <c r="AD34" s="2" t="n"/>
+      <c r="AE34" s="2" t="n"/>
+      <c r="AF34" s="2" t="inlineStr">
+        <is>
+          <t>Neumática</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="n"/>
+      <c r="AH34" s="2" t="n"/>
+      <c r="AI34" s="2" t="n"/>
+      <c r="AJ34" s="2" t="n"/>
+      <c r="AK34" s="2" t="n"/>
+      <c r="AL34" s="2" t="n"/>
+      <c r="AM34" s="2" t="n"/>
+      <c r="AN34" s="2" t="n"/>
+      <c r="AO34" s="2" t="n"/>
+      <c r="AP34" s="2" t="n"/>
+      <c r="AQ34" s="2" t="n"/>
+      <c r="AR34" s="2" t="n"/>
+      <c r="AS34" s="2" t="n"/>
+      <c r="AT34" s="2" t="n"/>
+      <c r="AU34" s="2" t="n"/>
+      <c r="AV34" s="2" t="n"/>
+      <c r="AW34" s="2" t="n"/>
+      <c r="AX34" s="2" t="n"/>
+      <c r="AY34" s="2" t="n"/>
+      <c r="AZ34" s="2" t="n"/>
+      <c r="BA34" s="2" t="n"/>
+      <c r="BB34" s="2" t="n"/>
+      <c r="BC34" s="2" t="n"/>
+      <c r="BD34" s="2" t="n"/>
+      <c r="BE34" s="2" t="n"/>
+      <c r="BF34" s="2" t="n"/>
+      <c r="BG34" s="2" t="n"/>
+      <c r="BH34" s="2" t="n"/>
+      <c r="BI34" s="2" t="n"/>
+      <c r="BJ34" s="2" t="n"/>
+      <c r="BK34" s="2" t="n"/>
+      <c r="BL34" s="2" t="n"/>
+      <c r="BM34" s="2" t="n"/>
+      <c r="BN34" s="2" t="n"/>
+      <c r="BO34" s="2" t="n"/>
+      <c r="BP34" s="2" t="n"/>
+      <c r="BQ34" s="2" t="n"/>
+      <c r="BR34" s="2" t="n"/>
+      <c r="BS34" s="2" t="n"/>
+      <c r="BT34" s="2" t="n"/>
+      <c r="BU34" s="2" t="n"/>
+      <c r="BV34" s="2" t="n"/>
+      <c r="BW34" s="2" t="n"/>
+      <c r="BX34" s="2" t="n"/>
+      <c r="BY34" s="2" t="n"/>
+      <c r="BZ34" s="2" t="n"/>
+      <c r="CA34" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="CB34" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="CC34" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="CD34" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="CE34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CF34" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="CG34" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="CH34" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="CI34" s="2" t="inlineStr">
+        <is>
+          <t>Husky 515</t>
+        </is>
+      </c>
+      <c r="CJ34" s="2" t="n"/>
+      <c r="CK34" s="2" t="n"/>
+      <c r="CL34" s="2" t="n"/>
+      <c r="CM34" s="2" t="n"/>
+      <c r="CN34" s="2" t="n"/>
+      <c r="CO34" s="2" t="n"/>
+      <c r="CP34" s="2" t="n"/>
+      <c r="CQ34" s="2" t="n"/>
+      <c r="CR34" s="2" t="n"/>
+      <c r="CS34" s="2" t="n"/>
+      <c r="CT34" s="2" t="n"/>
+      <c r="CU34" s="2" t="n"/>
+      <c r="CV34" s="2" t="n"/>
+      <c r="CW34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>802-P-01</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>EQUIPOS</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Bomba dosificadora de floculante</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Dosificación de Floculante</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Floculante</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>7 - 8</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Cuerpo: Polipropileno
+Diafragma PTFE</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
+      <c r="T35" s="2" t="n"/>
+      <c r="U35" s="2" t="n"/>
+      <c r="V35" s="2" t="n"/>
+      <c r="W35" s="2" t="n"/>
+      <c r="X35" s="2" t="n"/>
+      <c r="Y35" s="2" t="n"/>
+      <c r="Z35" s="2" t="n"/>
+      <c r="AA35" s="2" t="n"/>
+      <c r="AB35" s="2" t="n"/>
+      <c r="AC35" s="2" t="n"/>
+      <c r="AD35" s="2" t="n"/>
+      <c r="AE35" s="2" t="n"/>
+      <c r="AF35" s="2" t="inlineStr">
+        <is>
+          <t>Neumática</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="n"/>
+      <c r="AH35" s="2" t="n"/>
+      <c r="AI35" s="2" t="n"/>
+      <c r="AJ35" s="2" t="n"/>
+      <c r="AK35" s="2" t="n"/>
+      <c r="AL35" s="2" t="n"/>
+      <c r="AM35" s="2" t="n"/>
+      <c r="AN35" s="2" t="n"/>
+      <c r="AO35" s="2" t="n"/>
+      <c r="AP35" s="2" t="n"/>
+      <c r="AQ35" s="2" t="n"/>
+      <c r="AR35" s="2" t="n"/>
+      <c r="AS35" s="2" t="n"/>
+      <c r="AT35" s="2" t="n"/>
+      <c r="AU35" s="2" t="n"/>
+      <c r="AV35" s="2" t="n"/>
+      <c r="AW35" s="2" t="n"/>
+      <c r="AX35" s="2" t="n"/>
+      <c r="AY35" s="2" t="n"/>
+      <c r="AZ35" s="2" t="n"/>
+      <c r="BA35" s="2" t="n"/>
+      <c r="BB35" s="2" t="n"/>
+      <c r="BC35" s="2" t="n"/>
+      <c r="BD35" s="2" t="n"/>
+      <c r="BE35" s="2" t="n"/>
+      <c r="BF35" s="2" t="n"/>
+      <c r="BG35" s="2" t="n"/>
+      <c r="BH35" s="2" t="n"/>
+      <c r="BI35" s="2" t="n"/>
+      <c r="BJ35" s="2" t="n"/>
+      <c r="BK35" s="2" t="n"/>
+      <c r="BL35" s="2" t="n"/>
+      <c r="BM35" s="2" t="n"/>
+      <c r="BN35" s="2" t="n"/>
+      <c r="BO35" s="2" t="n"/>
+      <c r="BP35" s="2" t="n"/>
+      <c r="BQ35" s="2" t="n"/>
+      <c r="BR35" s="2" t="n"/>
+      <c r="BS35" s="2" t="n"/>
+      <c r="BT35" s="2" t="n"/>
+      <c r="BU35" s="2" t="n"/>
+      <c r="BV35" s="2" t="n"/>
+      <c r="BW35" s="2" t="n"/>
+      <c r="BX35" s="2" t="n"/>
+      <c r="BY35" s="2" t="n"/>
+      <c r="BZ35" s="2" t="n"/>
+      <c r="CA35" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="CB35" s="2" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="CC35" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="CD35" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="CE35" s="2" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="CF35" s="2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="CG35" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="CH35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CI35" s="2" t="inlineStr">
+        <is>
+          <t>Wilden p.025</t>
+        </is>
+      </c>
+      <c r="CJ35" s="2" t="n"/>
+      <c r="CK35" s="2" t="n"/>
+      <c r="CL35" s="2" t="n"/>
+      <c r="CM35" s="2" t="n"/>
+      <c r="CN35" s="2" t="n"/>
+      <c r="CO35" s="2" t="n"/>
+      <c r="CP35" s="2" t="n"/>
+      <c r="CQ35" s="2" t="n"/>
+      <c r="CR35" s="2" t="n"/>
+      <c r="CS35" s="2" t="n"/>
+      <c r="CT35" s="2" t="n"/>
+      <c r="CU35" s="2" t="n"/>
+      <c r="CV35" s="2" t="n"/>
+      <c r="CW35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>803-P-01</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>EQUIPOS</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Bomba dosificadora de deshidratante</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Dosificación de Deshidratante</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Discontinua</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Deshidratante</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>7 - 8</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>Cuerpo: Polipropileno
+Diafragma PTFE</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
+      <c r="T36" s="2" t="n"/>
+      <c r="U36" s="2" t="n"/>
+      <c r="V36" s="2" t="n"/>
+      <c r="W36" s="2" t="n"/>
+      <c r="X36" s="2" t="n"/>
+      <c r="Y36" s="2" t="n"/>
+      <c r="Z36" s="2" t="n"/>
+      <c r="AA36" s="2" t="n"/>
+      <c r="AB36" s="2" t="n"/>
+      <c r="AC36" s="2" t="n"/>
+      <c r="AD36" s="2" t="n"/>
+      <c r="AE36" s="2" t="n"/>
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>Neumática</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="n"/>
+      <c r="AH36" s="2" t="n"/>
+      <c r="AI36" s="2" t="n"/>
+      <c r="AJ36" s="2" t="n"/>
+      <c r="AK36" s="2" t="n"/>
+      <c r="AL36" s="2" t="n"/>
+      <c r="AM36" s="2" t="n"/>
+      <c r="AN36" s="2" t="n"/>
+      <c r="AO36" s="2" t="n"/>
+      <c r="AP36" s="2" t="n"/>
+      <c r="AQ36" s="2" t="n"/>
+      <c r="AR36" s="2" t="n"/>
+      <c r="AS36" s="2" t="n"/>
+      <c r="AT36" s="2" t="n"/>
+      <c r="AU36" s="2" t="n"/>
+      <c r="AV36" s="2" t="n"/>
+      <c r="AW36" s="2" t="n"/>
+      <c r="AX36" s="2" t="n"/>
+      <c r="AY36" s="2" t="n"/>
+      <c r="AZ36" s="2" t="n"/>
+      <c r="BA36" s="2" t="n"/>
+      <c r="BB36" s="2" t="n"/>
+      <c r="BC36" s="2" t="n"/>
+      <c r="BD36" s="2" t="n"/>
+      <c r="BE36" s="2" t="n"/>
+      <c r="BF36" s="2" t="n"/>
+      <c r="BG36" s="2" t="n"/>
+      <c r="BH36" s="2" t="n"/>
+      <c r="BI36" s="2" t="n"/>
+      <c r="BJ36" s="2" t="n"/>
+      <c r="BK36" s="2" t="n"/>
+      <c r="BL36" s="2" t="n"/>
+      <c r="BM36" s="2" t="n"/>
+      <c r="BN36" s="2" t="n"/>
+      <c r="BO36" s="2" t="n"/>
+      <c r="BP36" s="2" t="n"/>
+      <c r="BQ36" s="2" t="n"/>
+      <c r="BR36" s="2" t="n"/>
+      <c r="BS36" s="2" t="n"/>
+      <c r="BT36" s="2" t="n"/>
+      <c r="BU36" s="2" t="n"/>
+      <c r="BV36" s="2" t="n"/>
+      <c r="BW36" s="2" t="n"/>
+      <c r="BX36" s="2" t="n"/>
+      <c r="BY36" s="2" t="n"/>
+      <c r="BZ36" s="2" t="n"/>
+      <c r="CA36" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="CB36" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="CC36" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="CD36" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="CE36" s="2" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="CF36" s="2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="CG36" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="CH36" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CI36" s="2" t="inlineStr">
+        <is>
+          <t>Wilden p.025</t>
+        </is>
+      </c>
+      <c r="CJ36" s="2" t="n"/>
+      <c r="CK36" s="2" t="n"/>
+      <c r="CL36" s="2" t="n"/>
+      <c r="CM36" s="2" t="n"/>
+      <c r="CN36" s="2" t="n"/>
+      <c r="CO36" s="2" t="n"/>
+      <c r="CP36" s="2" t="n"/>
+      <c r="CQ36" s="2" t="n"/>
+      <c r="CR36" s="2" t="n"/>
+      <c r="CS36" s="2" t="n"/>
+      <c r="CT36" s="2" t="n"/>
+      <c r="CU36" s="2" t="n"/>
+      <c r="CV36" s="2" t="n"/>
+      <c r="CW36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>500-P-01</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>EQUIPOS</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Bomba de trasiego de agua filtrada a vertimiento final</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Trasiego de agua filtrada para vertimiento / retrolavado</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Agua residual no domestica</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>Cuerpo de la bomba, impulsor, cobertura del sello, carcasa AISI 304. AISI 303 (parte en contacto con líquido).</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Centrifuga horizontal</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>Succión: 1 1/4"                                                                                                       Descarga: 1"</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>Directo</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>CDX 120/106</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="n"/>
+      <c r="AE37" s="2" t="n"/>
+      <c r="AF37" s="2" t="n"/>
+      <c r="AG37" s="2" t="n"/>
+      <c r="AH37" s="2" t="n"/>
+      <c r="AI37" s="2" t="n"/>
+      <c r="AJ37" s="2" t="n"/>
+      <c r="AK37" s="2" t="n"/>
+      <c r="AL37" s="2" t="n"/>
+      <c r="AM37" s="2" t="n"/>
+      <c r="AN37" s="2" t="n"/>
+      <c r="AO37" s="2" t="n"/>
+      <c r="AP37" s="2" t="n"/>
+      <c r="AQ37" s="2" t="n"/>
+      <c r="AR37" s="2" t="n"/>
+      <c r="AS37" s="2" t="n"/>
+      <c r="AT37" s="2" t="n"/>
+      <c r="AU37" s="2" t="n"/>
+      <c r="AV37" s="2" t="n"/>
+      <c r="AW37" s="2" t="n"/>
+      <c r="AX37" s="2" t="n"/>
+      <c r="AY37" s="2" t="n"/>
+      <c r="AZ37" s="2" t="n"/>
+      <c r="BA37" s="2" t="n"/>
+      <c r="BB37" s="2" t="n"/>
+      <c r="BC37" s="2" t="n"/>
+      <c r="BD37" s="2" t="n"/>
+      <c r="BE37" s="2" t="n"/>
+      <c r="BF37" s="2" t="n"/>
+      <c r="BG37" s="2" t="n"/>
+      <c r="BH37" s="2" t="n"/>
+      <c r="BI37" s="2" t="n"/>
+      <c r="BJ37" s="2" t="n"/>
+      <c r="BK37" s="2" t="n"/>
+      <c r="BL37" s="2" t="n"/>
+      <c r="BM37" s="2" t="n"/>
+      <c r="BN37" s="2" t="n"/>
+      <c r="BO37" s="2" t="n"/>
+      <c r="BP37" s="2" t="n"/>
+      <c r="BQ37" s="2" t="n"/>
+      <c r="BR37" s="2" t="n"/>
+      <c r="BS37" s="2" t="n"/>
+      <c r="BT37" s="2" t="n"/>
+      <c r="BU37" s="2" t="n"/>
+      <c r="BV37" s="2" t="n"/>
+      <c r="BW37" s="2" t="n"/>
+      <c r="BX37" s="2" t="n"/>
+      <c r="BY37" s="2" t="n"/>
+      <c r="BZ37" s="2" t="n"/>
+      <c r="CA37" s="2" t="n"/>
+      <c r="CB37" s="2" t="n"/>
+      <c r="CC37" s="2" t="n"/>
+      <c r="CD37" s="2" t="n"/>
+      <c r="CE37" s="2" t="n"/>
+      <c r="CF37" s="2" t="n"/>
+      <c r="CG37" s="2" t="n"/>
+      <c r="CH37" s="2" t="n"/>
+      <c r="CI37" s="2" t="n"/>
+      <c r="CJ37" s="2" t="n"/>
+      <c r="CK37" s="2" t="n"/>
+      <c r="CL37" s="2" t="n"/>
+      <c r="CM37" s="2" t="n"/>
+      <c r="CN37" s="2" t="n"/>
+      <c r="CO37" s="2" t="n"/>
+      <c r="CP37" s="2" t="n"/>
+      <c r="CQ37" s="2" t="n"/>
+      <c r="CR37" s="2" t="n"/>
+      <c r="CS37" s="2" t="n"/>
+      <c r="CT37" s="2" t="n"/>
+      <c r="CU37" s="2" t="n"/>
+      <c r="CV37" s="2" t="n"/>
+      <c r="CW37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>600-P-01</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>EQUIPOS</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Bomba trasiego de lodos</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Trasiego del tanque de acondicionamiento de lodo 600-TK-02 a Filtro prensa</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Discontinua</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Lodos</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>Cuerpo: Polipropileno
+Diafragma PTFE</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="n"/>
+      <c r="S38" s="2" t="n"/>
+      <c r="T38" s="2" t="n"/>
+      <c r="U38" s="2" t="n"/>
+      <c r="V38" s="2" t="n"/>
+      <c r="W38" s="2" t="n"/>
+      <c r="X38" s="2" t="n"/>
+      <c r="Y38" s="2" t="n"/>
+      <c r="Z38" s="2" t="n"/>
+      <c r="AA38" s="2" t="n"/>
+      <c r="AB38" s="2" t="n"/>
+      <c r="AC38" s="2" t="n"/>
+      <c r="AD38" s="2" t="n"/>
+      <c r="AE38" s="2" t="n"/>
+      <c r="AF38" s="2" t="inlineStr">
+        <is>
+          <t>Neumática</t>
+        </is>
+      </c>
+      <c r="AG38" s="2" t="n"/>
+      <c r="AH38" s="2" t="n"/>
+      <c r="AI38" s="2" t="n"/>
+      <c r="AJ38" s="2" t="n"/>
+      <c r="AK38" s="2" t="n"/>
+      <c r="AL38" s="2" t="n"/>
+      <c r="AM38" s="2" t="n"/>
+      <c r="AN38" s="2" t="n"/>
+      <c r="AO38" s="2" t="n"/>
+      <c r="AP38" s="2" t="n"/>
+      <c r="AQ38" s="2" t="n"/>
+      <c r="AR38" s="2" t="n"/>
+      <c r="AS38" s="2" t="n"/>
+      <c r="AT38" s="2" t="n"/>
+      <c r="AU38" s="2" t="n"/>
+      <c r="AV38" s="2" t="n"/>
+      <c r="AW38" s="2" t="n"/>
+      <c r="AX38" s="2" t="n"/>
+      <c r="AY38" s="2" t="n"/>
+      <c r="AZ38" s="2" t="n"/>
+      <c r="BA38" s="2" t="n"/>
+      <c r="BB38" s="2" t="n"/>
+      <c r="BC38" s="2" t="n"/>
+      <c r="BD38" s="2" t="n"/>
+      <c r="BE38" s="2" t="n"/>
+      <c r="BF38" s="2" t="n"/>
+      <c r="BG38" s="2" t="n"/>
+      <c r="BH38" s="2" t="n"/>
+      <c r="BI38" s="2" t="n"/>
+      <c r="BJ38" s="2" t="n"/>
+      <c r="BK38" s="2" t="n"/>
+      <c r="BL38" s="2" t="n"/>
+      <c r="BM38" s="2" t="n"/>
+      <c r="BN38" s="2" t="n"/>
+      <c r="BO38" s="2" t="n"/>
+      <c r="BP38" s="2" t="n"/>
+      <c r="BQ38" s="2" t="n"/>
+      <c r="BR38" s="2" t="n"/>
+      <c r="BS38" s="2" t="n"/>
+      <c r="BT38" s="2" t="n"/>
+      <c r="BU38" s="2" t="n"/>
+      <c r="BV38" s="2" t="n"/>
+      <c r="BW38" s="2" t="n"/>
+      <c r="BX38" s="2" t="n"/>
+      <c r="BY38" s="2" t="n"/>
+      <c r="BZ38" s="2" t="n"/>
+      <c r="CA38" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="CB38" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="CC38" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="CD38" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="CE38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CF38" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="CG38" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="CH38" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="CI38" s="2" t="inlineStr">
+        <is>
+          <t>Husky 515</t>
+        </is>
+      </c>
+      <c r="CJ38" s="2" t="n"/>
+      <c r="CK38" s="2" t="n"/>
+      <c r="CL38" s="2" t="n"/>
+      <c r="CM38" s="2" t="n"/>
+      <c r="CN38" s="2" t="n"/>
+      <c r="CO38" s="2" t="n"/>
+      <c r="CP38" s="2" t="n"/>
+      <c r="CQ38" s="2" t="n"/>
+      <c r="CR38" s="2" t="n"/>
+      <c r="CS38" s="2" t="n"/>
+      <c r="CT38" s="2" t="n"/>
+      <c r="CU38" s="2" t="n"/>
+      <c r="CV38" s="2" t="n"/>
+      <c r="CW38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>600-SD-01</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>TANQUES</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Deshidratación de lodos</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Filtro tipo camara de lodos fisicoquímicos y biológicos</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Discontinua</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Lodo</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>6 - 8</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>Estructura en acero al carbón, telas en PP/PET</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="n"/>
+      <c r="U39" s="2" t="n"/>
+      <c r="V39" s="2" t="n"/>
+      <c r="W39" s="2" t="n"/>
+      <c r="X39" s="2" t="n"/>
+      <c r="Y39" s="2" t="n"/>
+      <c r="Z39" s="2" t="n"/>
+      <c r="AA39" s="2" t="n"/>
+      <c r="AB39" s="2" t="n"/>
+      <c r="AC39" s="2" t="n"/>
+      <c r="AD39" s="2" t="n"/>
+      <c r="AE39" s="2" t="n"/>
+      <c r="AF39" s="2" t="inlineStr">
+        <is>
+          <t>Camara de cierre hidráulico</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="n"/>
+      <c r="AH39" s="2" t="n"/>
+      <c r="AI39" s="2" t="n"/>
+      <c r="AJ39" s="2" t="n"/>
+      <c r="AK39" s="2" t="n"/>
+      <c r="AL39" s="2" t="n"/>
+      <c r="AM39" s="2" t="n"/>
+      <c r="AN39" s="2" t="n"/>
+      <c r="AO39" s="2" t="n"/>
+      <c r="AP39" s="2" t="n"/>
+      <c r="AQ39" s="2" t="n"/>
+      <c r="AR39" s="2" t="n"/>
+      <c r="AS39" s="2" t="n"/>
+      <c r="AT39" s="2" t="n"/>
+      <c r="AU39" s="2" t="n"/>
+      <c r="AV39" s="2" t="n"/>
+      <c r="AW39" s="2" t="n"/>
+      <c r="AX39" s="2" t="n"/>
+      <c r="AY39" s="2" t="n"/>
+      <c r="AZ39" s="2" t="n"/>
+      <c r="BA39" s="2" t="n"/>
+      <c r="BB39" s="2" t="n"/>
+      <c r="BC39" s="2" t="n"/>
+      <c r="BD39" s="2" t="n"/>
+      <c r="BE39" s="2" t="n"/>
+      <c r="BF39" s="2" t="n"/>
+      <c r="BG39" s="2" t="n"/>
+      <c r="BH39" s="2" t="n"/>
+      <c r="BI39" s="2" t="n"/>
+      <c r="BJ39" s="2" t="n"/>
+      <c r="BK39" s="2" t="n"/>
+      <c r="BL39" s="2" t="n"/>
+      <c r="BM39" s="2" t="n"/>
+      <c r="BN39" s="2" t="n"/>
+      <c r="BO39" s="2" t="n"/>
+      <c r="BP39" s="2" t="n"/>
+      <c r="BQ39" s="2" t="n"/>
+      <c r="BR39" s="2" t="n"/>
+      <c r="BS39" s="2" t="n"/>
+      <c r="BT39" s="2" t="n"/>
+      <c r="BU39" s="2" t="n"/>
+      <c r="BV39" s="2" t="n"/>
+      <c r="BW39" s="2" t="n"/>
+      <c r="BX39" s="2" t="n"/>
+      <c r="BY39" s="2" t="n"/>
+      <c r="BZ39" s="2" t="n"/>
+      <c r="CA39" s="2" t="n"/>
+      <c r="CB39" s="2" t="n"/>
+      <c r="CC39" s="2" t="n"/>
+      <c r="CD39" s="2" t="n"/>
+      <c r="CE39" s="2" t="n"/>
+      <c r="CF39" s="2" t="n"/>
+      <c r="CG39" s="2" t="n"/>
+      <c r="CH39" s="2" t="n"/>
+      <c r="CI39" s="2" t="inlineStr">
+        <is>
+          <t>XMY20/630-24U</t>
+        </is>
+      </c>
+      <c r="CJ39" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="CK39" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="CL39" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="CM39" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="CN39" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="CO39" s="2" t="inlineStr">
+        <is>
+          <t>17 - 19</t>
+        </is>
+      </c>
+      <c r="CP39" s="2" t="inlineStr">
+        <is>
+          <t>Malla 250/400/500</t>
+        </is>
+      </c>
+      <c r="CQ39" s="2" t="n"/>
+      <c r="CR39" s="2" t="n"/>
+      <c r="CS39" s="2" t="n"/>
+      <c r="CT39" s="2" t="n"/>
+      <c r="CU39" s="2" t="n"/>
+      <c r="CV39" s="2" t="n"/>
+      <c r="CW39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>801-P-01</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>EQUIPOS</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Bomba dosificadora</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Dosificación de Soda Cáustica</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Soda Cáustica</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>Cabezal de dosificación: cloruro de polivinilo (PVC) 
+Bola de válvula: Cerámica
+ Junta de estanqueidad: EPDM</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="n"/>
+      <c r="S40" s="2" t="n"/>
+      <c r="T40" s="2" t="n"/>
+      <c r="U40" s="2" t="n"/>
+      <c r="V40" s="2" t="n"/>
+      <c r="W40" s="2" t="n"/>
+      <c r="X40" s="2" t="n"/>
+      <c r="Y40" s="2" t="n"/>
+      <c r="Z40" s="2" t="n"/>
+      <c r="AA40" s="2" t="n"/>
+      <c r="AB40" s="2" t="n"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>GRUNDFOS DDE 6-10</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="n"/>
+      <c r="AE40" s="2" t="n"/>
+      <c r="AF40" s="2" t="inlineStr">
+        <is>
+          <t>Diafragma eléctrica</t>
+        </is>
+      </c>
+      <c r="AG40" s="2" t="n"/>
+      <c r="AH40" s="2" t="n"/>
+      <c r="AI40" s="2" t="n"/>
+      <c r="AJ40" s="2" t="n"/>
+      <c r="AK40" s="2" t="n"/>
+      <c r="AL40" s="2" t="n"/>
+      <c r="AM40" s="2" t="n"/>
+      <c r="AN40" s="2" t="n"/>
+      <c r="AO40" s="2" t="n"/>
+      <c r="AP40" s="2" t="n"/>
+      <c r="AQ40" s="2" t="n"/>
+      <c r="AR40" s="2" t="n"/>
+      <c r="AS40" s="2" t="n"/>
+      <c r="AT40" s="2" t="n"/>
+      <c r="AU40" s="2" t="n"/>
+      <c r="AV40" s="2" t="n"/>
+      <c r="AW40" s="2" t="n"/>
+      <c r="AX40" s="2" t="n"/>
+      <c r="AY40" s="2" t="n"/>
+      <c r="AZ40" s="2" t="n"/>
+      <c r="BA40" s="2" t="n"/>
+      <c r="BB40" s="2" t="n"/>
+      <c r="BC40" s="2" t="n"/>
+      <c r="BD40" s="2" t="n"/>
+      <c r="BE40" s="2" t="n"/>
+      <c r="BF40" s="2" t="n"/>
+      <c r="BG40" s="2" t="n"/>
+      <c r="BH40" s="2" t="n"/>
+      <c r="BI40" s="2" t="n"/>
+      <c r="BJ40" s="2" t="n"/>
+      <c r="BK40" s="2" t="n"/>
+      <c r="BL40" s="2" t="n"/>
+      <c r="BM40" s="2" t="n"/>
+      <c r="BN40" s="2" t="n"/>
+      <c r="BO40" s="2" t="n"/>
+      <c r="BP40" s="2" t="n"/>
+      <c r="BQ40" s="2" t="n"/>
+      <c r="BR40" s="2" t="n"/>
+      <c r="BS40" s="2" t="n"/>
+      <c r="BT40" s="2" t="n"/>
+      <c r="BU40" s="2" t="n"/>
+      <c r="BV40" s="2" t="n"/>
+      <c r="BW40" s="2" t="n"/>
+      <c r="BX40" s="2" t="n"/>
+      <c r="BY40" s="2" t="n"/>
+      <c r="BZ40" s="2" t="n"/>
+      <c r="CA40" s="2" t="n"/>
+      <c r="CB40" s="2" t="n"/>
+      <c r="CC40" s="2" t="n"/>
+      <c r="CD40" s="2" t="n"/>
+      <c r="CE40" s="2" t="n"/>
+      <c r="CF40" s="2" t="n"/>
+      <c r="CG40" s="2" t="n"/>
+      <c r="CH40" s="2" t="n"/>
+      <c r="CI40" s="2" t="n"/>
+      <c r="CJ40" s="2" t="n"/>
+      <c r="CK40" s="2" t="n"/>
+      <c r="CL40" s="2" t="n"/>
+      <c r="CM40" s="2" t="n"/>
+      <c r="CN40" s="2" t="n"/>
+      <c r="CO40" s="2" t="n"/>
+      <c r="CP40" s="2" t="n"/>
+      <c r="CQ40" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="CR40" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CS40" s="2" t="inlineStr">
+        <is>
+          <t>IP65 / TYPE 4X</t>
+        </is>
+      </c>
+      <c r="CT40" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="CU40" s="2" t="inlineStr">
+        <is>
+          <t>10 - 45</t>
+        </is>
+      </c>
+      <c r="CV40" s="2" t="n"/>
+      <c r="CW40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>807-P-01</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>EQUIPOS</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Bomba dosificadora</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Dosificación de nutrientes</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Nutrientes</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>Cabezal de dosificación: cloruro de polivinilo (PVC) 
+Bola de válvula: Cerámica
+ Junta de estanqueidad: EPDM</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="n"/>
+      <c r="S41" s="2" t="n"/>
+      <c r="T41" s="2" t="n"/>
+      <c r="U41" s="2" t="n"/>
+      <c r="V41" s="2" t="n"/>
+      <c r="W41" s="2" t="n"/>
+      <c r="X41" s="2" t="n"/>
+      <c r="Y41" s="2" t="n"/>
+      <c r="Z41" s="2" t="n"/>
+      <c r="AA41" s="2" t="n"/>
+      <c r="AB41" s="2" t="n"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>GRUNDFOS DDE 15 - 4</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="n"/>
+      <c r="AE41" s="2" t="n"/>
+      <c r="AF41" s="2" t="inlineStr">
+        <is>
+          <t>Diafragma eléctrica</t>
+        </is>
+      </c>
+      <c r="AG41" s="2" t="n"/>
+      <c r="AH41" s="2" t="n"/>
+      <c r="AI41" s="2" t="n"/>
+      <c r="AJ41" s="2" t="n"/>
+      <c r="AK41" s="2" t="n"/>
+      <c r="AL41" s="2" t="n"/>
+      <c r="AM41" s="2" t="n"/>
+      <c r="AN41" s="2" t="n"/>
+      <c r="AO41" s="2" t="n"/>
+      <c r="AP41" s="2" t="n"/>
+      <c r="AQ41" s="2" t="n"/>
+      <c r="AR41" s="2" t="n"/>
+      <c r="AS41" s="2" t="n"/>
+      <c r="AT41" s="2" t="n"/>
+      <c r="AU41" s="2" t="n"/>
+      <c r="AV41" s="2" t="n"/>
+      <c r="AW41" s="2" t="n"/>
+      <c r="AX41" s="2" t="n"/>
+      <c r="AY41" s="2" t="n"/>
+      <c r="AZ41" s="2" t="n"/>
+      <c r="BA41" s="2" t="n"/>
+      <c r="BB41" s="2" t="n"/>
+      <c r="BC41" s="2" t="n"/>
+      <c r="BD41" s="2" t="n"/>
+      <c r="BE41" s="2" t="n"/>
+      <c r="BF41" s="2" t="n"/>
+      <c r="BG41" s="2" t="n"/>
+      <c r="BH41" s="2" t="n"/>
+      <c r="BI41" s="2" t="n"/>
+      <c r="BJ41" s="2" t="n"/>
+      <c r="BK41" s="2" t="n"/>
+      <c r="BL41" s="2" t="n"/>
+      <c r="BM41" s="2" t="n"/>
+      <c r="BN41" s="2" t="n"/>
+      <c r="BO41" s="2" t="n"/>
+      <c r="BP41" s="2" t="n"/>
+      <c r="BQ41" s="2" t="n"/>
+      <c r="BR41" s="2" t="n"/>
+      <c r="BS41" s="2" t="n"/>
+      <c r="BT41" s="2" t="n"/>
+      <c r="BU41" s="2" t="n"/>
+      <c r="BV41" s="2" t="n"/>
+      <c r="BW41" s="2" t="n"/>
+      <c r="BX41" s="2" t="n"/>
+      <c r="BY41" s="2" t="n"/>
+      <c r="BZ41" s="2" t="n"/>
+      <c r="CA41" s="2" t="n"/>
+      <c r="CB41" s="2" t="n"/>
+      <c r="CC41" s="2" t="n"/>
+      <c r="CD41" s="2" t="n"/>
+      <c r="CE41" s="2" t="n"/>
+      <c r="CF41" s="2" t="n"/>
+      <c r="CG41" s="2" t="n"/>
+      <c r="CH41" s="2" t="n"/>
+      <c r="CI41" s="2" t="n"/>
+      <c r="CJ41" s="2" t="n"/>
+      <c r="CK41" s="2" t="n"/>
+      <c r="CL41" s="2" t="n"/>
+      <c r="CM41" s="2" t="n"/>
+      <c r="CN41" s="2" t="n"/>
+      <c r="CO41" s="2" t="n"/>
+      <c r="CP41" s="2" t="n"/>
+      <c r="CQ41" s="2" t="n"/>
+      <c r="CR41" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="CS41" s="2" t="inlineStr">
+        <is>
+          <t>IP65 / TYPE 4X</t>
+        </is>
+      </c>
+      <c r="CT41" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="CU41" s="2" t="inlineStr">
+        <is>
+          <t>10 - 45</t>
+        </is>
+      </c>
+      <c r="CV41" s="2" t="n"/>
+      <c r="CW41" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/plantilla_sitio.xlsx
+++ b/plantilla_sitio.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW41"/>
+  <dimension ref="A1:CW43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <col width="22" customWidth="1" min="29" max="29"/>
     <col width="24" customWidth="1" min="30" max="30"/>
     <col width="27" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="50" customWidth="1" min="32" max="32"/>
     <col width="25" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="18" customWidth="1" min="35" max="35"/>
@@ -7907,6 +7907,284 @@
       <c r="CV41" s="2" t="n"/>
       <c r="CW41" s="2" t="n"/>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>802-SV-001</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>INSTRUMENTOS</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Válvula solenoide</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Ingreso/cierre de  aire de la bomba neumatica 802-P-01 (Floculante)</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Aire comprimido</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
+      <c r="Q42" s="2" t="n"/>
+      <c r="R42" s="2" t="n"/>
+      <c r="S42" s="2" t="n"/>
+      <c r="T42" s="2" t="n"/>
+      <c r="U42" s="2" t="n"/>
+      <c r="V42" s="2" t="n"/>
+      <c r="W42" s="2" t="n"/>
+      <c r="X42" s="2" t="n"/>
+      <c r="Y42" s="2" t="n"/>
+      <c r="Z42" s="2" t="n"/>
+      <c r="AA42" s="2" t="n"/>
+      <c r="AB42" s="2" t="n"/>
+      <c r="AC42" s="2" t="n"/>
+      <c r="AD42" s="2" t="n"/>
+      <c r="AE42" s="2" t="n"/>
+      <c r="AF42" s="2" t="inlineStr">
+        <is>
+          <t>Válvula solenoide con actuador neumático. Presión de suministro de aire: 29 ---145</t>
+        </is>
+      </c>
+      <c r="AG42" s="2" t="n"/>
+      <c r="AH42" s="2" t="n"/>
+      <c r="AI42" s="2" t="n"/>
+      <c r="AJ42" s="2" t="n"/>
+      <c r="AK42" s="2" t="n"/>
+      <c r="AL42" s="2" t="n"/>
+      <c r="AM42" s="2" t="n"/>
+      <c r="AN42" s="2" t="n"/>
+      <c r="AO42" s="2" t="n"/>
+      <c r="AP42" s="2" t="n"/>
+      <c r="AQ42" s="2" t="n"/>
+      <c r="AR42" s="2" t="n"/>
+      <c r="AS42" s="2" t="n"/>
+      <c r="AT42" s="2" t="n"/>
+      <c r="AU42" s="2" t="n"/>
+      <c r="AV42" s="2" t="n"/>
+      <c r="AW42" s="2" t="n"/>
+      <c r="AX42" s="2" t="n"/>
+      <c r="AY42" s="2" t="n"/>
+      <c r="AZ42" s="2" t="n"/>
+      <c r="BA42" s="2" t="n"/>
+      <c r="BB42" s="2" t="n"/>
+      <c r="BC42" s="2" t="n"/>
+      <c r="BD42" s="2" t="n"/>
+      <c r="BE42" s="2" t="n"/>
+      <c r="BF42" s="2" t="n"/>
+      <c r="BG42" s="2" t="n"/>
+      <c r="BH42" s="2" t="n"/>
+      <c r="BI42" s="2" t="n"/>
+      <c r="BJ42" s="2" t="n"/>
+      <c r="BK42" s="2" t="n"/>
+      <c r="BL42" s="2" t="n"/>
+      <c r="BM42" s="2" t="n"/>
+      <c r="BN42" s="2" t="n"/>
+      <c r="BO42" s="2" t="n"/>
+      <c r="BP42" s="2" t="n"/>
+      <c r="BQ42" s="2" t="n"/>
+      <c r="BR42" s="2" t="n"/>
+      <c r="BS42" s="2" t="n"/>
+      <c r="BT42" s="2" t="n"/>
+      <c r="BU42" s="2" t="n"/>
+      <c r="BV42" s="2" t="n"/>
+      <c r="BW42" s="2" t="n"/>
+      <c r="BX42" s="2" t="n"/>
+      <c r="BY42" s="2" t="n"/>
+      <c r="BZ42" s="2" t="n"/>
+      <c r="CA42" s="2" t="n"/>
+      <c r="CB42" s="2" t="n"/>
+      <c r="CC42" s="2" t="n"/>
+      <c r="CD42" s="2" t="n"/>
+      <c r="CE42" s="2" t="n"/>
+      <c r="CF42" s="2" t="n"/>
+      <c r="CG42" s="2" t="n"/>
+      <c r="CH42" s="2" t="n"/>
+      <c r="CI42" s="2" t="n"/>
+      <c r="CJ42" s="2" t="n"/>
+      <c r="CK42" s="2" t="n"/>
+      <c r="CL42" s="2" t="n"/>
+      <c r="CM42" s="2" t="n"/>
+      <c r="CN42" s="2" t="n"/>
+      <c r="CO42" s="2" t="n"/>
+      <c r="CP42" s="2" t="n"/>
+      <c r="CQ42" s="2" t="n"/>
+      <c r="CR42" s="2" t="n"/>
+      <c r="CS42" s="2" t="n"/>
+      <c r="CT42" s="2" t="n"/>
+      <c r="CU42" s="2" t="inlineStr">
+        <is>
+          <t>20 - 25</t>
+        </is>
+      </c>
+      <c r="CV42" s="2" t="n"/>
+      <c r="CW42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>600-SV-01</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>INSTRUMENTOS</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Válvula solenoide</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Ingreso/cierre de  aire Línea de aire comprimido hacia bomba 600-P-01 (Trasiego de lodos)</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Discontinua</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Aire comprimido</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n"/>
+      <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="n"/>
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="n"/>
+      <c r="U43" s="2" t="n"/>
+      <c r="V43" s="2" t="n"/>
+      <c r="W43" s="2" t="n"/>
+      <c r="X43" s="2" t="n"/>
+      <c r="Y43" s="2" t="n"/>
+      <c r="Z43" s="2" t="n"/>
+      <c r="AA43" s="2" t="n"/>
+      <c r="AB43" s="2" t="n"/>
+      <c r="AC43" s="2" t="n"/>
+      <c r="AD43" s="2" t="n"/>
+      <c r="AE43" s="2" t="n"/>
+      <c r="AF43" s="2" t="inlineStr">
+        <is>
+          <t>Válvula solenoide con actuador eléctrico</t>
+        </is>
+      </c>
+      <c r="AG43" s="2" t="n"/>
+      <c r="AH43" s="2" t="n"/>
+      <c r="AI43" s="2" t="n"/>
+      <c r="AJ43" s="2" t="n"/>
+      <c r="AK43" s="2" t="n"/>
+      <c r="AL43" s="2" t="n"/>
+      <c r="AM43" s="2" t="n"/>
+      <c r="AN43" s="2" t="n"/>
+      <c r="AO43" s="2" t="n"/>
+      <c r="AP43" s="2" t="n"/>
+      <c r="AQ43" s="2" t="n"/>
+      <c r="AR43" s="2" t="n"/>
+      <c r="AS43" s="2" t="n"/>
+      <c r="AT43" s="2" t="n"/>
+      <c r="AU43" s="2" t="n"/>
+      <c r="AV43" s="2" t="n"/>
+      <c r="AW43" s="2" t="n"/>
+      <c r="AX43" s="2" t="n"/>
+      <c r="AY43" s="2" t="n"/>
+      <c r="AZ43" s="2" t="n"/>
+      <c r="BA43" s="2" t="n"/>
+      <c r="BB43" s="2" t="n"/>
+      <c r="BC43" s="2" t="n"/>
+      <c r="BD43" s="2" t="n"/>
+      <c r="BE43" s="2" t="n"/>
+      <c r="BF43" s="2" t="n"/>
+      <c r="BG43" s="2" t="n"/>
+      <c r="BH43" s="2" t="n"/>
+      <c r="BI43" s="2" t="n"/>
+      <c r="BJ43" s="2" t="n"/>
+      <c r="BK43" s="2" t="n"/>
+      <c r="BL43" s="2" t="n"/>
+      <c r="BM43" s="2" t="n"/>
+      <c r="BN43" s="2" t="n"/>
+      <c r="BO43" s="2" t="n"/>
+      <c r="BP43" s="2" t="n"/>
+      <c r="BQ43" s="2" t="n"/>
+      <c r="BR43" s="2" t="n"/>
+      <c r="BS43" s="2" t="n"/>
+      <c r="BT43" s="2" t="n"/>
+      <c r="BU43" s="2" t="n"/>
+      <c r="BV43" s="2" t="n"/>
+      <c r="BW43" s="2" t="n"/>
+      <c r="BX43" s="2" t="n"/>
+      <c r="BY43" s="2" t="n"/>
+      <c r="BZ43" s="2" t="n"/>
+      <c r="CA43" s="2" t="n"/>
+      <c r="CB43" s="2" t="n"/>
+      <c r="CC43" s="2" t="n"/>
+      <c r="CD43" s="2" t="n"/>
+      <c r="CE43" s="2" t="n"/>
+      <c r="CF43" s="2" t="n"/>
+      <c r="CG43" s="2" t="n"/>
+      <c r="CH43" s="2" t="n"/>
+      <c r="CI43" s="2" t="n"/>
+      <c r="CJ43" s="2" t="n"/>
+      <c r="CK43" s="2" t="n"/>
+      <c r="CL43" s="2" t="n"/>
+      <c r="CM43" s="2" t="n"/>
+      <c r="CN43" s="2" t="n"/>
+      <c r="CO43" s="2" t="n"/>
+      <c r="CP43" s="2" t="n"/>
+      <c r="CQ43" s="2" t="n"/>
+      <c r="CR43" s="2" t="n"/>
+      <c r="CS43" s="2" t="n"/>
+      <c r="CT43" s="2" t="n"/>
+      <c r="CU43" s="2" t="inlineStr">
+        <is>
+          <t>20 - 25</t>
+        </is>
+      </c>
+      <c r="CV43" s="2" t="n"/>
+      <c r="CW43" s="2" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Categoría inválida" error="Debe ser una de: EQUIPOS, INSTRUMENTOS, TANQUES" promptTitle="Categoría" prompt="Selecciona: EQUIPOS, INSTRUMENTOS, TANQUES" type="list">
